--- a/data_fetching/Entsoe/Hydro_Production.xlsx
+++ b/data_fetching/Entsoe/Hydro_Production.xlsx
@@ -390,7 +390,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E47"/>
+  <dimension ref="A1:E36"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:5">
@@ -412,784 +412,597 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="2">
-        <v>46269</v>
+        <v>46278</v>
       </c>
       <c r="B2">
-        <v>867</v>
+        <v>776</v>
       </c>
       <c r="C2">
-        <v>436</v>
+        <v>428</v>
       </c>
       <c r="D2">
-        <v>1377.148621412836</v>
+        <v>978.7880539749887</v>
       </c>
       <c r="E2">
-        <v>1303</v>
+        <v>1204</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="2">
-        <v>46269.01041666666</v>
+        <v>46278.01041666666</v>
       </c>
       <c r="B3">
-        <v>867</v>
+        <v>772</v>
       </c>
       <c r="C3">
-        <v>434</v>
+        <v>427</v>
       </c>
       <c r="D3">
-        <v>1366.368006472928</v>
+        <v>933.6272096183804</v>
       </c>
       <c r="E3">
-        <v>1301</v>
+        <v>1199</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="2">
-        <v>46269.02083333334</v>
+        <v>46278.02083333334</v>
       </c>
       <c r="B4">
-        <v>866</v>
+        <v>768</v>
       </c>
       <c r="C4">
-        <v>435</v>
+        <v>428</v>
       </c>
       <c r="D4">
-        <v>1355.58739153302</v>
+        <v>888.4663652617724</v>
       </c>
       <c r="E4">
-        <v>1301</v>
+        <v>1196</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="2">
-        <v>46269.03125</v>
+        <v>46278.03125</v>
       </c>
       <c r="B5">
-        <v>863</v>
+        <v>768</v>
       </c>
       <c r="C5">
-        <v>433</v>
+        <v>427</v>
       </c>
       <c r="D5">
-        <v>1344.806776593112</v>
+        <v>843.3055209051641</v>
       </c>
       <c r="E5">
-        <v>1296</v>
+        <v>1195</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="2">
-        <v>46269.04166666666</v>
+        <v>46278.04166666666</v>
       </c>
       <c r="B6">
-        <v>867</v>
+        <v>706</v>
       </c>
       <c r="C6">
-        <v>416</v>
+        <v>423</v>
       </c>
       <c r="D6">
-        <v>1334.026161653204</v>
+        <v>798.1446765485559</v>
       </c>
       <c r="E6">
-        <v>1283</v>
+        <v>1129</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="2">
-        <v>46269.05208333334</v>
+        <v>46278.05208333334</v>
       </c>
       <c r="B7">
-        <v>864</v>
+        <v>688</v>
       </c>
       <c r="C7">
-        <v>416</v>
+        <v>411</v>
       </c>
       <c r="D7">
-        <v>1327.710767858109</v>
+        <v>803.4415860656142</v>
       </c>
       <c r="E7">
-        <v>1280</v>
+        <v>1099</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="2">
-        <v>46269.0625</v>
+        <v>46278.0625</v>
       </c>
       <c r="B8">
-        <v>864</v>
+        <v>688</v>
       </c>
       <c r="C8">
-        <v>415</v>
+        <v>403</v>
       </c>
       <c r="D8">
-        <v>1321.395374063014</v>
+        <v>808.7384955826724</v>
       </c>
       <c r="E8">
-        <v>1279</v>
+        <v>1091</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="2">
-        <v>46269.07291666666</v>
+        <v>46278.07291666666</v>
       </c>
       <c r="B9">
-        <v>866</v>
+        <v>687</v>
       </c>
       <c r="C9">
-        <v>413</v>
+        <v>402</v>
       </c>
       <c r="D9">
-        <v>1315.079980267919</v>
+        <v>814.0354050997306</v>
       </c>
       <c r="E9">
-        <v>1279</v>
+        <v>1089</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="2">
-        <v>46269.08333333334</v>
+        <v>46278.08333333334</v>
       </c>
       <c r="B10">
-        <v>853</v>
+        <v>681</v>
       </c>
       <c r="C10">
-        <v>408</v>
+        <v>415</v>
       </c>
       <c r="D10">
-        <v>1308.764586472824</v>
+        <v>819.3323146167888</v>
       </c>
       <c r="E10">
-        <v>1261</v>
+        <v>1096</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="2">
-        <v>46269.09375</v>
+        <v>46278.09375</v>
       </c>
       <c r="B11">
-        <v>853</v>
+        <v>680</v>
       </c>
       <c r="C11">
-        <v>406</v>
+        <v>417</v>
       </c>
       <c r="D11">
-        <v>1301.756669953941</v>
+        <v>823.8281928580509</v>
       </c>
       <c r="E11">
-        <v>1259</v>
+        <v>1097</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="2">
-        <v>46269.10416666666</v>
+        <v>46278.10416666666</v>
       </c>
       <c r="B12">
-        <v>854</v>
+        <v>680</v>
       </c>
       <c r="C12">
-        <v>408</v>
+        <v>416</v>
       </c>
       <c r="D12">
-        <v>1294.748753435058</v>
+        <v>828.324071099313</v>
       </c>
       <c r="E12">
-        <v>1262</v>
+        <v>1096</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="2">
-        <v>46269.11458333334</v>
+        <v>46278.11458333334</v>
       </c>
       <c r="B13">
-        <v>854</v>
+        <v>678</v>
       </c>
       <c r="C13">
         <v>418</v>
       </c>
       <c r="D13">
-        <v>1287.740836916174</v>
+        <v>832.8199493405751</v>
       </c>
       <c r="E13">
-        <v>1272</v>
+        <v>1096</v>
       </c>
     </row>
     <row r="14" spans="1:5">
       <c r="A14" s="2">
-        <v>46269.125</v>
+        <v>46278.125</v>
       </c>
       <c r="B14">
-        <v>855</v>
+        <v>204</v>
       </c>
       <c r="C14">
-        <v>416</v>
+        <v>340</v>
       </c>
       <c r="D14">
-        <v>1280.732920397291</v>
+        <v>837.3158275818372</v>
       </c>
       <c r="E14">
-        <v>1271</v>
+        <v>544</v>
       </c>
     </row>
     <row r="15" spans="1:5">
       <c r="A15" s="2">
-        <v>46269.13541666666</v>
+        <v>46278.13541666666</v>
       </c>
       <c r="B15">
-        <v>855</v>
+        <v>183</v>
       </c>
       <c r="C15">
-        <v>417</v>
+        <v>336</v>
       </c>
       <c r="D15">
-        <v>1269.259782733705</v>
+        <v>854.440577287466</v>
       </c>
       <c r="E15">
-        <v>1272</v>
+        <v>519</v>
       </c>
     </row>
     <row r="16" spans="1:5">
       <c r="A16" s="2">
-        <v>46269.14583333334</v>
+        <v>46278.14583333334</v>
       </c>
       <c r="B16">
-        <v>854</v>
+        <v>183</v>
       </c>
       <c r="C16">
-        <v>409</v>
+        <v>335</v>
       </c>
       <c r="D16">
-        <v>1257.786645070119</v>
+        <v>871.5653269930948</v>
       </c>
       <c r="E16">
-        <v>1263</v>
+        <v>518</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="2">
-        <v>46269.15625</v>
+        <v>46278.15625</v>
       </c>
       <c r="B17">
-        <v>861</v>
+        <v>213</v>
       </c>
       <c r="C17">
-        <v>418</v>
+        <v>336</v>
       </c>
       <c r="D17">
-        <v>1246.313507406534</v>
+        <v>888.6900766987236</v>
       </c>
       <c r="E17">
-        <v>1279</v>
+        <v>549</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="2">
-        <v>46269.16666666666</v>
+        <v>46278.16666666666</v>
       </c>
       <c r="B18">
-        <v>884</v>
+        <v>660</v>
       </c>
       <c r="C18">
-        <v>413</v>
+        <v>389</v>
       </c>
       <c r="D18">
-        <v>1234.840369742948</v>
+        <v>905.8148264043524</v>
       </c>
       <c r="E18">
-        <v>1297</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="2">
-        <v>46269.17708333334</v>
+        <v>46278.17708333334</v>
       </c>
       <c r="B19">
-        <v>884</v>
+        <v>673</v>
       </c>
       <c r="C19">
-        <v>405</v>
+        <v>399</v>
       </c>
       <c r="D19">
-        <v>1269.16675729347</v>
+        <v>919.0210177072843</v>
       </c>
       <c r="E19">
-        <v>1289</v>
+        <v>1072</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="2">
-        <v>46269.1875</v>
+        <v>46278.1875</v>
       </c>
       <c r="B20">
-        <v>885</v>
+        <v>674</v>
       </c>
       <c r="C20">
-        <v>405</v>
+        <v>400</v>
       </c>
       <c r="D20">
-        <v>1303.493144843992</v>
+        <v>932.227209010216</v>
       </c>
       <c r="E20">
-        <v>1290</v>
+        <v>1074</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="2">
-        <v>46269.19791666666</v>
+        <v>46278.19791666666</v>
       </c>
       <c r="B21">
-        <v>884</v>
+        <v>680</v>
       </c>
       <c r="C21">
-        <v>404</v>
+        <v>401</v>
       </c>
       <c r="D21">
-        <v>1337.819532394514</v>
+        <v>945.4334003131479</v>
       </c>
       <c r="E21">
-        <v>1288</v>
+        <v>1081</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="2">
-        <v>46269.20833333334</v>
+        <v>46278.20833333334</v>
       </c>
       <c r="B22">
-        <v>924</v>
+        <v>655</v>
       </c>
       <c r="C22">
-        <v>419</v>
+        <v>441</v>
       </c>
       <c r="D22">
-        <v>1372.145919945036</v>
+        <v>958.6395916160798</v>
       </c>
       <c r="E22">
-        <v>1343</v>
+        <v>1096</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="2">
-        <v>46269.21875</v>
+        <v>46278.21875</v>
       </c>
       <c r="B23">
-        <v>931</v>
+        <v>664</v>
       </c>
       <c r="C23">
-        <v>413</v>
+        <v>441</v>
       </c>
       <c r="D23">
-        <v>1429.790684585443</v>
+        <v>987.180841125434</v>
       </c>
       <c r="E23">
-        <v>1344</v>
+        <v>1105</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="2">
-        <v>46269.22916666666</v>
+        <v>46278.22916666666</v>
       </c>
       <c r="B24">
-        <v>958</v>
+        <v>668</v>
       </c>
       <c r="C24">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="D24">
-        <v>1487.435449225851</v>
+        <v>1015.722090634788</v>
       </c>
       <c r="E24">
-        <v>1384</v>
+        <v>1101</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="2">
-        <v>46269.23958333334</v>
+        <v>46278.23958333334</v>
       </c>
       <c r="B25">
-        <v>960</v>
+        <v>652</v>
       </c>
       <c r="C25">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="D25">
-        <v>1545.080213866258</v>
+        <v>1044.263340144143</v>
       </c>
       <c r="E25">
-        <v>1394</v>
+        <v>1085</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="2">
-        <v>46269.25</v>
+        <v>46278.25</v>
       </c>
       <c r="B26">
-        <v>1029</v>
+        <v>681</v>
       </c>
       <c r="C26">
-        <v>536</v>
+        <v>447</v>
       </c>
       <c r="D26">
-        <v>1602.724978506666</v>
+        <v>1072.804589653497</v>
       </c>
       <c r="E26">
-        <v>1565</v>
+        <v>1128</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="2">
-        <v>46269.26041666666</v>
+        <v>46278.26041666666</v>
       </c>
       <c r="B27">
-        <v>1001</v>
+        <v>678</v>
       </c>
       <c r="C27">
-        <v>541</v>
+        <v>451</v>
       </c>
       <c r="D27">
-        <v>1566.56909062574</v>
+        <v>1076.737581052474</v>
       </c>
       <c r="E27">
-        <v>1542</v>
+        <v>1129</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="2">
-        <v>46269.27083333334</v>
+        <v>46278.27083333334</v>
       </c>
       <c r="B28">
-        <v>1002</v>
+        <v>679</v>
       </c>
       <c r="C28">
-        <v>533</v>
+        <v>452</v>
       </c>
       <c r="D28">
-        <v>1530.413202744815</v>
+        <v>1080.670572451451</v>
       </c>
       <c r="E28">
-        <v>1535</v>
+        <v>1131</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="2">
-        <v>46269.28125</v>
+        <v>46278.28125</v>
       </c>
       <c r="B29">
-        <v>991</v>
+        <v>677</v>
       </c>
       <c r="C29">
-        <v>537</v>
+        <v>453</v>
       </c>
       <c r="D29">
-        <v>1494.257314863889</v>
+        <v>1084.603563850428</v>
       </c>
       <c r="E29">
-        <v>1528</v>
+        <v>1130</v>
       </c>
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="2">
-        <v>46269.29166666666</v>
+        <v>46278.29166666666</v>
       </c>
       <c r="B30">
-        <v>964</v>
+        <v>679</v>
       </c>
       <c r="C30">
-        <v>572</v>
+        <v>443</v>
       </c>
       <c r="D30">
-        <v>1458.101426982964</v>
+        <v>1088.536555249405</v>
       </c>
       <c r="E30">
-        <v>1536</v>
+        <v>1122</v>
       </c>
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="2">
-        <v>46269.30208333334</v>
+        <v>46278.30208333334</v>
       </c>
       <c r="B31">
-        <v>939</v>
+        <v>683</v>
       </c>
       <c r="C31">
-        <v>565</v>
+        <v>444</v>
       </c>
       <c r="D31">
-        <v>1416.591408192344</v>
+        <v>1059.995305739786</v>
       </c>
       <c r="E31">
-        <v>1504</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="2">
-        <v>46269.3125</v>
+        <v>46278.3125</v>
       </c>
       <c r="B32">
-        <v>932</v>
+        <v>685</v>
       </c>
       <c r="C32">
-        <v>565</v>
+        <v>444</v>
       </c>
       <c r="D32">
-        <v>1375.081389401725</v>
+        <v>1031.454056230166</v>
       </c>
       <c r="E32">
-        <v>1497</v>
+        <v>1129</v>
       </c>
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="2">
-        <v>46269.32291666666</v>
+        <v>46278.32291666666</v>
       </c>
       <c r="B33">
-        <v>931</v>
+        <v>681</v>
       </c>
       <c r="C33">
-        <v>559</v>
+        <v>446</v>
       </c>
       <c r="D33">
-        <v>1333.571370611106</v>
+        <v>1002.912806720547</v>
       </c>
       <c r="E33">
-        <v>1490</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="2">
-        <v>46269.33333333334</v>
+        <v>46278.33333333334</v>
       </c>
       <c r="B34">
-        <v>899</v>
+        <v>535</v>
       </c>
       <c r="C34">
-        <v>455</v>
+        <v>445</v>
       </c>
       <c r="D34">
-        <v>1292.061351820487</v>
+        <v>974.3715572109278</v>
       </c>
       <c r="E34">
-        <v>1354</v>
+        <v>980</v>
       </c>
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="2">
-        <v>46269.34375</v>
+        <v>46278.34375</v>
       </c>
       <c r="B35">
-        <v>936</v>
+        <v>545</v>
       </c>
       <c r="C35">
-        <v>449</v>
+        <v>435</v>
       </c>
       <c r="D35">
-        <v>1135.633905511096</v>
+        <v>874.5818231485108</v>
       </c>
       <c r="E35">
-        <v>1385</v>
+        <v>980</v>
       </c>
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="2">
-        <v>46269.35416666666</v>
+        <v>46278.35416666666</v>
       </c>
       <c r="B36">
-        <v>787</v>
+        <v>454</v>
       </c>
       <c r="C36">
-        <v>452</v>
+        <v>433</v>
       </c>
       <c r="D36">
-        <v>979.2064592017061</v>
+        <v>774.7920890860939</v>
       </c>
       <c r="E36">
-        <v>1239</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37" s="2">
-        <v>46269.36458333334</v>
-      </c>
-      <c r="B37">
-        <v>766</v>
-      </c>
-      <c r="C37">
-        <v>451</v>
-      </c>
-      <c r="D37">
-        <v>822.7790128923159</v>
-      </c>
-      <c r="E37">
-        <v>1217</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38" s="2">
-        <v>46269.375</v>
-      </c>
-      <c r="B38">
-        <v>245</v>
-      </c>
-      <c r="C38">
-        <v>298</v>
-      </c>
-      <c r="D38">
-        <v>666.3515665829257</v>
-      </c>
-      <c r="E38">
-        <v>543</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
-      <c r="A39" s="2">
-        <v>46269.38541666666</v>
-      </c>
-      <c r="B39">
-        <v>228</v>
-      </c>
-      <c r="C39">
-        <v>289</v>
-      </c>
-      <c r="D39">
-        <v>611.6836160391559</v>
-      </c>
-      <c r="E39">
-        <v>517</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
-      <c r="A40" s="2">
-        <v>46269.39583333334</v>
-      </c>
-      <c r="B40">
-        <v>222</v>
-      </c>
-      <c r="C40">
-        <v>289</v>
-      </c>
-      <c r="D40">
-        <v>557.0156654953862</v>
-      </c>
-      <c r="E40">
-        <v>511</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
-      <c r="A41" s="2">
-        <v>46269.40625</v>
-      </c>
-      <c r="B41">
-        <v>221</v>
-      </c>
-      <c r="C41">
-        <v>289</v>
-      </c>
-      <c r="D41">
-        <v>502.3477149516165</v>
-      </c>
-      <c r="E41">
-        <v>510</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
-      <c r="A42" s="2">
-        <v>46269.41666666666</v>
-      </c>
-      <c r="B42">
-        <v>173</v>
-      </c>
-      <c r="C42">
-        <v>247</v>
-      </c>
-      <c r="D42">
-        <v>447.6797644078467</v>
-      </c>
-      <c r="E42">
-        <v>420</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
-      <c r="A43" s="2">
-        <v>46269.42708333334</v>
-      </c>
-      <c r="B43">
-        <v>162</v>
-      </c>
-      <c r="C43">
-        <v>243</v>
-      </c>
-      <c r="D43">
-        <v>444.8166480719765</v>
-      </c>
-      <c r="E43">
-        <v>405</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
-      <c r="A44" s="2">
-        <v>46269.4375</v>
-      </c>
-      <c r="B44">
-        <v>162</v>
-      </c>
-      <c r="C44">
-        <v>243</v>
-      </c>
-      <c r="D44">
-        <v>441.9535317361063</v>
-      </c>
-      <c r="E44">
-        <v>405</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5">
-      <c r="A45" s="2">
-        <v>46269.44791666666</v>
-      </c>
-      <c r="B45">
-        <v>69</v>
-      </c>
-      <c r="C45">
-        <v>244</v>
-      </c>
-      <c r="D45">
-        <v>439.0904154002361</v>
-      </c>
-      <c r="E45">
-        <v>313</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5">
-      <c r="A46" s="2">
-        <v>46269.45833333334</v>
-      </c>
-      <c r="B46">
-        <v>101</v>
-      </c>
-      <c r="C46">
-        <v>250</v>
-      </c>
-      <c r="D46">
-        <v>436.2272990643659</v>
-      </c>
-      <c r="E46">
-        <v>351</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5">
-      <c r="A47" s="2">
-        <v>46269.46875</v>
-      </c>
-      <c r="B47">
-        <v>0</v>
-      </c>
-      <c r="C47">
-        <v>248</v>
-      </c>
-      <c r="D47">
-        <v>428.2064388597516</v>
-      </c>
-      <c r="E47">
-        <v>248</v>
+        <v>887</v>
       </c>
     </row>
   </sheetData>

--- a/data_fetching/Entsoe/Hydro_Production.xlsx
+++ b/data_fetching/Entsoe/Hydro_Production.xlsx
@@ -390,7 +390,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E36"/>
+  <dimension ref="A1:E41"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:5">
@@ -412,597 +412,682 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="2">
-        <v>46278</v>
+        <v>46283</v>
       </c>
       <c r="B2">
-        <v>776</v>
+        <v>393</v>
       </c>
       <c r="C2">
-        <v>428</v>
+        <v>689</v>
       </c>
       <c r="D2">
-        <v>978.7880539749887</v>
+        <v>1428.71402386456</v>
       </c>
       <c r="E2">
-        <v>1204</v>
+        <v>1082</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="2">
-        <v>46278.01041666666</v>
+        <v>46283.01041666666</v>
       </c>
       <c r="B3">
-        <v>772</v>
+        <v>387</v>
       </c>
       <c r="C3">
-        <v>427</v>
+        <v>690</v>
       </c>
       <c r="D3">
-        <v>933.6272096183804</v>
+        <v>1420.126080559834</v>
       </c>
       <c r="E3">
-        <v>1199</v>
+        <v>1077</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="2">
-        <v>46278.02083333334</v>
+        <v>46283.02083333334</v>
       </c>
       <c r="B4">
-        <v>768</v>
+        <v>386</v>
       </c>
       <c r="C4">
-        <v>428</v>
+        <v>690</v>
       </c>
       <c r="D4">
-        <v>888.4663652617724</v>
+        <v>1411.538137255108</v>
       </c>
       <c r="E4">
-        <v>1196</v>
+        <v>1076</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="2">
-        <v>46278.03125</v>
+        <v>46283.03125</v>
       </c>
       <c r="B5">
-        <v>768</v>
+        <v>386</v>
       </c>
       <c r="C5">
-        <v>427</v>
+        <v>690</v>
       </c>
       <c r="D5">
-        <v>843.3055209051641</v>
+        <v>1402.950193950381</v>
       </c>
       <c r="E5">
-        <v>1195</v>
+        <v>1076</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="2">
-        <v>46278.04166666666</v>
+        <v>46283.04166666666</v>
       </c>
       <c r="B6">
-        <v>706</v>
+        <v>170</v>
       </c>
       <c r="C6">
-        <v>423</v>
+        <v>420</v>
       </c>
       <c r="D6">
-        <v>798.1446765485559</v>
+        <v>1394.362250645655</v>
       </c>
       <c r="E6">
-        <v>1129</v>
+        <v>590</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="2">
-        <v>46278.05208333334</v>
+        <v>46283.05208333334</v>
       </c>
       <c r="B7">
-        <v>688</v>
+        <v>161</v>
       </c>
       <c r="C7">
-        <v>411</v>
+        <v>385</v>
       </c>
       <c r="D7">
-        <v>803.4415860656142</v>
+        <v>1397.313715647757</v>
       </c>
       <c r="E7">
-        <v>1099</v>
+        <v>546</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="2">
-        <v>46278.0625</v>
+        <v>46283.0625</v>
       </c>
       <c r="B8">
-        <v>688</v>
+        <v>159</v>
       </c>
       <c r="C8">
-        <v>403</v>
+        <v>385</v>
       </c>
       <c r="D8">
-        <v>808.7384955826724</v>
+        <v>1400.265180649858</v>
       </c>
       <c r="E8">
-        <v>1091</v>
+        <v>544</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="2">
-        <v>46278.07291666666</v>
+        <v>46283.07291666666</v>
       </c>
       <c r="B9">
-        <v>687</v>
+        <v>159</v>
       </c>
       <c r="C9">
-        <v>402</v>
+        <v>384</v>
       </c>
       <c r="D9">
-        <v>814.0354050997306</v>
+        <v>1403.21664565196</v>
       </c>
       <c r="E9">
-        <v>1089</v>
+        <v>543</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="2">
-        <v>46278.08333333334</v>
+        <v>46283.08333333334</v>
       </c>
       <c r="B10">
-        <v>681</v>
+        <v>219</v>
       </c>
       <c r="C10">
-        <v>415</v>
+        <v>423</v>
       </c>
       <c r="D10">
-        <v>819.3323146167888</v>
+        <v>1406.168110654062</v>
       </c>
       <c r="E10">
-        <v>1096</v>
+        <v>642</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="2">
-        <v>46278.09375</v>
+        <v>46283.09375</v>
       </c>
       <c r="B11">
-        <v>680</v>
+        <v>222</v>
       </c>
       <c r="C11">
-        <v>417</v>
+        <v>426</v>
       </c>
       <c r="D11">
-        <v>823.8281928580509</v>
+        <v>1379.246240652195</v>
       </c>
       <c r="E11">
-        <v>1097</v>
+        <v>648</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="2">
-        <v>46278.10416666666</v>
+        <v>46283.10416666666</v>
       </c>
       <c r="B12">
-        <v>680</v>
+        <v>221</v>
       </c>
       <c r="C12">
-        <v>416</v>
+        <v>424</v>
       </c>
       <c r="D12">
-        <v>828.324071099313</v>
+        <v>1352.324370650328</v>
       </c>
       <c r="E12">
-        <v>1096</v>
+        <v>645</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="2">
-        <v>46278.11458333334</v>
+        <v>46283.11458333334</v>
       </c>
       <c r="B13">
-        <v>678</v>
+        <v>232</v>
       </c>
       <c r="C13">
-        <v>418</v>
+        <v>426</v>
       </c>
       <c r="D13">
-        <v>832.8199493405751</v>
+        <v>1325.402500648461</v>
       </c>
       <c r="E13">
-        <v>1096</v>
+        <v>658</v>
       </c>
     </row>
     <row r="14" spans="1:5">
       <c r="A14" s="2">
-        <v>46278.125</v>
+        <v>46283.125</v>
       </c>
       <c r="B14">
-        <v>204</v>
+        <v>325</v>
       </c>
       <c r="C14">
-        <v>340</v>
+        <v>425</v>
       </c>
       <c r="D14">
-        <v>837.3158275818372</v>
+        <v>1298.480630646593</v>
       </c>
       <c r="E14">
-        <v>544</v>
+        <v>750</v>
       </c>
     </row>
     <row r="15" spans="1:5">
       <c r="A15" s="2">
-        <v>46278.13541666666</v>
+        <v>46283.13541666666</v>
       </c>
       <c r="B15">
-        <v>183</v>
+        <v>324</v>
       </c>
       <c r="C15">
-        <v>336</v>
+        <v>426</v>
       </c>
       <c r="D15">
-        <v>854.440577287466</v>
+        <v>1322.225576514254</v>
       </c>
       <c r="E15">
-        <v>519</v>
+        <v>750</v>
       </c>
     </row>
     <row r="16" spans="1:5">
       <c r="A16" s="2">
-        <v>46278.14583333334</v>
+        <v>46283.14583333334</v>
       </c>
       <c r="B16">
-        <v>183</v>
+        <v>324</v>
       </c>
       <c r="C16">
-        <v>335</v>
+        <v>425</v>
       </c>
       <c r="D16">
-        <v>871.5653269930948</v>
+        <v>1345.970522381914</v>
       </c>
       <c r="E16">
-        <v>518</v>
+        <v>749</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="2">
-        <v>46278.15625</v>
+        <v>46283.15625</v>
       </c>
       <c r="B17">
-        <v>213</v>
+        <v>343</v>
       </c>
       <c r="C17">
-        <v>336</v>
+        <v>425</v>
       </c>
       <c r="D17">
-        <v>888.6900766987236</v>
+        <v>1369.715468249575</v>
       </c>
       <c r="E17">
-        <v>549</v>
+        <v>768</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="2">
-        <v>46278.16666666666</v>
+        <v>46283.16666666666</v>
       </c>
       <c r="B18">
-        <v>660</v>
+        <v>524</v>
       </c>
       <c r="C18">
-        <v>389</v>
+        <v>423</v>
       </c>
       <c r="D18">
-        <v>905.8148264043524</v>
+        <v>1393.460414117235</v>
       </c>
       <c r="E18">
-        <v>1049</v>
+        <v>947</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="2">
-        <v>46278.17708333334</v>
+        <v>46283.17708333334</v>
       </c>
       <c r="B19">
-        <v>673</v>
+        <v>526</v>
       </c>
       <c r="C19">
-        <v>399</v>
+        <v>424</v>
       </c>
       <c r="D19">
-        <v>919.0210177072843</v>
+        <v>1405.72744053222</v>
       </c>
       <c r="E19">
-        <v>1072</v>
+        <v>950</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="2">
-        <v>46278.1875</v>
+        <v>46283.1875</v>
       </c>
       <c r="B20">
-        <v>674</v>
+        <v>525</v>
       </c>
       <c r="C20">
-        <v>400</v>
+        <v>423</v>
       </c>
       <c r="D20">
-        <v>932.227209010216</v>
+        <v>1417.994466947205</v>
       </c>
       <c r="E20">
-        <v>1074</v>
+        <v>948</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="2">
-        <v>46278.19791666666</v>
+        <v>46283.19791666666</v>
       </c>
       <c r="B21">
-        <v>680</v>
+        <v>533</v>
       </c>
       <c r="C21">
-        <v>401</v>
+        <v>425</v>
       </c>
       <c r="D21">
-        <v>945.4334003131479</v>
+        <v>1430.26149336219</v>
       </c>
       <c r="E21">
-        <v>1081</v>
+        <v>958</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="2">
-        <v>46278.20833333334</v>
+        <v>46283.20833333334</v>
       </c>
       <c r="B22">
-        <v>655</v>
+        <v>705</v>
       </c>
       <c r="C22">
-        <v>441</v>
+        <v>449</v>
       </c>
       <c r="D22">
-        <v>958.6395916160798</v>
+        <v>1442.528519777175</v>
       </c>
       <c r="E22">
-        <v>1096</v>
+        <v>1154</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="2">
-        <v>46278.21875</v>
+        <v>46283.21875</v>
       </c>
       <c r="B23">
-        <v>664</v>
+        <v>726</v>
       </c>
       <c r="C23">
-        <v>441</v>
+        <v>461</v>
       </c>
       <c r="D23">
-        <v>987.180841125434</v>
+        <v>1479.780517286268</v>
       </c>
       <c r="E23">
-        <v>1105</v>
+        <v>1187</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="2">
-        <v>46278.22916666666</v>
+        <v>46283.22916666666</v>
       </c>
       <c r="B24">
-        <v>668</v>
+        <v>723</v>
       </c>
       <c r="C24">
-        <v>433</v>
+        <v>556</v>
       </c>
       <c r="D24">
-        <v>1015.722090634788</v>
+        <v>1517.032514795362</v>
       </c>
       <c r="E24">
-        <v>1101</v>
+        <v>1279</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="2">
-        <v>46278.23958333334</v>
+        <v>46283.23958333334</v>
       </c>
       <c r="B25">
-        <v>652</v>
+        <v>737</v>
       </c>
       <c r="C25">
-        <v>433</v>
+        <v>551</v>
       </c>
       <c r="D25">
-        <v>1044.263340144143</v>
+        <v>1554.284512304456</v>
       </c>
       <c r="E25">
-        <v>1085</v>
+        <v>1288</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="2">
-        <v>46278.25</v>
+        <v>46283.25</v>
       </c>
       <c r="B26">
-        <v>681</v>
+        <v>773</v>
       </c>
       <c r="C26">
-        <v>447</v>
+        <v>663</v>
       </c>
       <c r="D26">
-        <v>1072.804589653497</v>
+        <v>1591.53650981355</v>
       </c>
       <c r="E26">
-        <v>1128</v>
+        <v>1436</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="2">
-        <v>46278.26041666666</v>
+        <v>46283.26041666666</v>
       </c>
       <c r="B27">
-        <v>678</v>
+        <v>777</v>
       </c>
       <c r="C27">
-        <v>451</v>
+        <v>667</v>
       </c>
       <c r="D27">
-        <v>1076.737581052474</v>
+        <v>1595.461548340578</v>
       </c>
       <c r="E27">
-        <v>1129</v>
+        <v>1444</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="2">
-        <v>46278.27083333334</v>
+        <v>46283.27083333334</v>
       </c>
       <c r="B28">
-        <v>679</v>
+        <v>772</v>
       </c>
       <c r="C28">
-        <v>452</v>
+        <v>666</v>
       </c>
       <c r="D28">
-        <v>1080.670572451451</v>
+        <v>1599.386586867606</v>
       </c>
       <c r="E28">
-        <v>1131</v>
+        <v>1438</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="2">
-        <v>46278.28125</v>
+        <v>46283.28125</v>
       </c>
       <c r="B29">
-        <v>677</v>
+        <v>761</v>
       </c>
       <c r="C29">
-        <v>453</v>
+        <v>666</v>
       </c>
       <c r="D29">
-        <v>1084.603563850428</v>
+        <v>1603.311625394634</v>
       </c>
       <c r="E29">
-        <v>1130</v>
+        <v>1427</v>
       </c>
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="2">
-        <v>46278.29166666666</v>
+        <v>46283.29166666666</v>
       </c>
       <c r="B30">
-        <v>679</v>
+        <v>805</v>
       </c>
       <c r="C30">
-        <v>443</v>
+        <v>665</v>
       </c>
       <c r="D30">
-        <v>1088.536555249405</v>
+        <v>1607.236663921662</v>
       </c>
       <c r="E30">
-        <v>1122</v>
+        <v>1470</v>
       </c>
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="2">
-        <v>46278.30208333334</v>
+        <v>46283.30208333334</v>
       </c>
       <c r="B31">
-        <v>683</v>
+        <v>829</v>
       </c>
       <c r="C31">
-        <v>444</v>
+        <v>648</v>
       </c>
       <c r="D31">
-        <v>1059.995305739786</v>
+        <v>1565.291017207909</v>
       </c>
       <c r="E31">
-        <v>1127</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="2">
-        <v>46278.3125</v>
+        <v>46283.3125</v>
       </c>
       <c r="B32">
-        <v>685</v>
+        <v>829</v>
       </c>
       <c r="C32">
-        <v>444</v>
+        <v>648</v>
       </c>
       <c r="D32">
-        <v>1031.454056230166</v>
+        <v>1523.345370494157</v>
       </c>
       <c r="E32">
-        <v>1129</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="2">
-        <v>46278.32291666666</v>
+        <v>46283.32291666666</v>
       </c>
       <c r="B33">
-        <v>681</v>
+        <v>829</v>
       </c>
       <c r="C33">
-        <v>446</v>
+        <v>648</v>
       </c>
       <c r="D33">
-        <v>1002.912806720547</v>
+        <v>1481.399723780405</v>
       </c>
       <c r="E33">
-        <v>1127</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="2">
-        <v>46278.33333333334</v>
+        <v>46283.33333333334</v>
       </c>
       <c r="B34">
-        <v>535</v>
+        <v>829</v>
       </c>
       <c r="C34">
-        <v>445</v>
+        <v>648</v>
       </c>
       <c r="D34">
-        <v>974.3715572109278</v>
+        <v>1439.454077066652</v>
       </c>
       <c r="E34">
-        <v>980</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="2">
-        <v>46278.34375</v>
+        <v>46283.34375</v>
       </c>
       <c r="B35">
-        <v>545</v>
+        <v>829</v>
       </c>
       <c r="C35">
-        <v>435</v>
+        <v>648</v>
       </c>
       <c r="D35">
-        <v>874.5818231485108</v>
+        <v>1278.240549469183</v>
       </c>
       <c r="E35">
-        <v>980</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="2">
-        <v>46278.35416666666</v>
+        <v>46283.35416666666</v>
       </c>
       <c r="B36">
-        <v>454</v>
+        <v>102</v>
       </c>
       <c r="C36">
-        <v>433</v>
+        <v>522</v>
       </c>
       <c r="D36">
-        <v>774.7920890860939</v>
+        <v>1117.027021871714</v>
       </c>
       <c r="E36">
-        <v>887</v>
+        <v>624</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="2">
+        <v>46283.36458333334</v>
+      </c>
+      <c r="B37">
+        <v>77</v>
+      </c>
+      <c r="C37">
+        <v>519</v>
+      </c>
+      <c r="D37">
+        <v>955.8134942742454</v>
+      </c>
+      <c r="E37">
+        <v>596</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="2">
+        <v>46283.375</v>
+      </c>
+      <c r="B38">
+        <v>61</v>
+      </c>
+      <c r="C38">
+        <v>332</v>
+      </c>
+      <c r="D38">
+        <v>794.5999666767764</v>
+      </c>
+      <c r="E38">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="2">
+        <v>46283.38541666666</v>
+      </c>
+      <c r="B39">
+        <v>60</v>
+      </c>
+      <c r="C39">
+        <v>306</v>
+      </c>
+      <c r="D39">
+        <v>729.8317069084943</v>
+      </c>
+      <c r="E39">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="2">
+        <v>46283.39583333334</v>
+      </c>
+      <c r="B40">
+        <v>59</v>
+      </c>
+      <c r="C40">
+        <v>305</v>
+      </c>
+      <c r="D40">
+        <v>665.0634471402122</v>
+      </c>
+      <c r="E40">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="2">
+        <v>46283.40625</v>
+      </c>
+      <c r="B41">
+        <v>58</v>
+      </c>
+      <c r="C41">
+        <v>304</v>
+      </c>
+      <c r="D41">
+        <v>600.2951873719301</v>
+      </c>
+      <c r="E41">
+        <v>362</v>
       </c>
     </row>
   </sheetData>

--- a/data_fetching/Entsoe/Hydro_Production.xlsx
+++ b/data_fetching/Entsoe/Hydro_Production.xlsx
@@ -390,7 +390,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E41"/>
+  <dimension ref="A1:E39"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:5">
@@ -412,682 +412,648 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="2">
-        <v>46283</v>
+        <v>46285</v>
       </c>
       <c r="B2">
-        <v>393</v>
+        <v>560</v>
       </c>
       <c r="C2">
-        <v>689</v>
+        <v>616</v>
       </c>
       <c r="D2">
-        <v>1428.71402386456</v>
+        <v>1239.957761143239</v>
       </c>
       <c r="E2">
-        <v>1082</v>
+        <v>1176</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="2">
-        <v>46283.01041666666</v>
+        <v>46285.01041666666</v>
       </c>
       <c r="B3">
-        <v>387</v>
+        <v>566</v>
       </c>
       <c r="C3">
-        <v>690</v>
+        <v>616</v>
       </c>
       <c r="D3">
-        <v>1420.126080559834</v>
+        <v>1206.843014594079</v>
       </c>
       <c r="E3">
-        <v>1077</v>
+        <v>1182</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="2">
-        <v>46283.02083333334</v>
+        <v>46285.02083333334</v>
       </c>
       <c r="B4">
-        <v>386</v>
+        <v>566</v>
       </c>
       <c r="C4">
-        <v>690</v>
+        <v>617</v>
       </c>
       <c r="D4">
-        <v>1411.538137255108</v>
+        <v>1173.72826804492</v>
       </c>
       <c r="E4">
-        <v>1076</v>
+        <v>1183</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="2">
-        <v>46283.03125</v>
+        <v>46285.03125</v>
       </c>
       <c r="B5">
-        <v>386</v>
+        <v>582</v>
       </c>
       <c r="C5">
-        <v>690</v>
+        <v>617</v>
       </c>
       <c r="D5">
-        <v>1402.950193950381</v>
+        <v>1140.61352149576</v>
       </c>
       <c r="E5">
-        <v>1076</v>
+        <v>1199</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="2">
-        <v>46283.04166666666</v>
+        <v>46285.04166666666</v>
       </c>
       <c r="B6">
-        <v>170</v>
+        <v>655</v>
       </c>
       <c r="C6">
-        <v>420</v>
+        <v>518</v>
       </c>
       <c r="D6">
-        <v>1394.362250645655</v>
+        <v>1107.4987749466</v>
       </c>
       <c r="E6">
-        <v>590</v>
+        <v>1173</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="2">
-        <v>46283.05208333334</v>
+        <v>46285.05208333334</v>
       </c>
       <c r="B7">
-        <v>161</v>
+        <v>655</v>
       </c>
       <c r="C7">
-        <v>385</v>
+        <v>503</v>
       </c>
       <c r="D7">
-        <v>1397.313715647757</v>
+        <v>1114.004345461215</v>
       </c>
       <c r="E7">
-        <v>546</v>
+        <v>1158</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="2">
-        <v>46283.0625</v>
+        <v>46285.0625</v>
       </c>
       <c r="B8">
-        <v>159</v>
+        <v>655</v>
       </c>
       <c r="C8">
-        <v>385</v>
+        <v>502</v>
       </c>
       <c r="D8">
-        <v>1400.265180649858</v>
+        <v>1120.509915975829</v>
       </c>
       <c r="E8">
-        <v>544</v>
+        <v>1157</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="2">
-        <v>46283.07291666666</v>
+        <v>46285.07291666666</v>
       </c>
       <c r="B9">
-        <v>159</v>
+        <v>655</v>
       </c>
       <c r="C9">
-        <v>384</v>
+        <v>502</v>
       </c>
       <c r="D9">
-        <v>1403.21664565196</v>
+        <v>1127.015486490443</v>
       </c>
       <c r="E9">
-        <v>543</v>
+        <v>1157</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="2">
-        <v>46283.08333333334</v>
+        <v>46285.08333333334</v>
       </c>
       <c r="B10">
-        <v>219</v>
+        <v>606</v>
       </c>
       <c r="C10">
-        <v>423</v>
+        <v>502</v>
       </c>
       <c r="D10">
-        <v>1406.168110654062</v>
+        <v>1133.521057005057</v>
       </c>
       <c r="E10">
-        <v>642</v>
+        <v>1108</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="2">
-        <v>46283.09375</v>
+        <v>46285.09375</v>
       </c>
       <c r="B11">
-        <v>222</v>
+        <v>606</v>
       </c>
       <c r="C11">
-        <v>426</v>
+        <v>502</v>
       </c>
       <c r="D11">
-        <v>1379.246240652195</v>
+        <v>1111.875611378341</v>
       </c>
       <c r="E11">
-        <v>648</v>
+        <v>1108</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="2">
-        <v>46283.10416666666</v>
+        <v>46285.10416666666</v>
       </c>
       <c r="B12">
-        <v>221</v>
+        <v>606</v>
       </c>
       <c r="C12">
-        <v>424</v>
+        <v>502</v>
       </c>
       <c r="D12">
-        <v>1352.324370650328</v>
+        <v>1090.230165751624</v>
       </c>
       <c r="E12">
-        <v>645</v>
+        <v>1108</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="2">
-        <v>46283.11458333334</v>
+        <v>46285.11458333334</v>
       </c>
       <c r="B13">
-        <v>232</v>
+        <v>606</v>
       </c>
       <c r="C13">
-        <v>426</v>
+        <v>502</v>
       </c>
       <c r="D13">
-        <v>1325.402500648461</v>
+        <v>1068.584720124908</v>
       </c>
       <c r="E13">
-        <v>658</v>
+        <v>1108</v>
       </c>
     </row>
     <row r="14" spans="1:5">
       <c r="A14" s="2">
-        <v>46283.125</v>
+        <v>46285.125</v>
       </c>
       <c r="B14">
-        <v>325</v>
+        <v>607</v>
       </c>
       <c r="C14">
-        <v>425</v>
+        <v>502</v>
       </c>
       <c r="D14">
-        <v>1298.480630646593</v>
+        <v>1046.939274498192</v>
       </c>
       <c r="E14">
-        <v>750</v>
+        <v>1109</v>
       </c>
     </row>
     <row r="15" spans="1:5">
       <c r="A15" s="2">
-        <v>46283.13541666666</v>
+        <v>46285.13541666666</v>
       </c>
       <c r="B15">
-        <v>324</v>
+        <v>606</v>
       </c>
       <c r="C15">
-        <v>426</v>
+        <v>501</v>
       </c>
       <c r="D15">
-        <v>1322.225576514254</v>
+        <v>1082.560754640249</v>
       </c>
       <c r="E15">
-        <v>750</v>
+        <v>1107</v>
       </c>
     </row>
     <row r="16" spans="1:5">
       <c r="A16" s="2">
-        <v>46283.14583333334</v>
+        <v>46285.14583333334</v>
       </c>
       <c r="B16">
-        <v>324</v>
+        <v>607</v>
       </c>
       <c r="C16">
-        <v>425</v>
+        <v>502</v>
       </c>
       <c r="D16">
-        <v>1345.970522381914</v>
+        <v>1118.182234782306</v>
       </c>
       <c r="E16">
-        <v>749</v>
+        <v>1109</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="2">
-        <v>46283.15625</v>
+        <v>46285.15625</v>
       </c>
       <c r="B17">
-        <v>343</v>
+        <v>606</v>
       </c>
       <c r="C17">
-        <v>425</v>
+        <v>501</v>
       </c>
       <c r="D17">
-        <v>1369.715468249575</v>
+        <v>1153.803714924363</v>
       </c>
       <c r="E17">
-        <v>768</v>
+        <v>1107</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="2">
-        <v>46283.16666666666</v>
+        <v>46285.16666666666</v>
       </c>
       <c r="B18">
-        <v>524</v>
+        <v>589</v>
       </c>
       <c r="C18">
-        <v>423</v>
+        <v>510</v>
       </c>
       <c r="D18">
-        <v>1393.460414117235</v>
+        <v>1189.42519506642</v>
       </c>
       <c r="E18">
-        <v>947</v>
+        <v>1099</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="2">
-        <v>46283.17708333334</v>
+        <v>46285.17708333334</v>
       </c>
       <c r="B19">
-        <v>526</v>
+        <v>588</v>
       </c>
       <c r="C19">
-        <v>424</v>
+        <v>515</v>
       </c>
       <c r="D19">
-        <v>1405.72744053222</v>
+        <v>1210.483746717071</v>
       </c>
       <c r="E19">
-        <v>950</v>
+        <v>1103</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="2">
-        <v>46283.1875</v>
+        <v>46285.1875</v>
       </c>
       <c r="B20">
-        <v>525</v>
+        <v>588</v>
       </c>
       <c r="C20">
-        <v>423</v>
+        <v>515</v>
       </c>
       <c r="D20">
-        <v>1417.994466947205</v>
+        <v>1231.542298367722</v>
       </c>
       <c r="E20">
-        <v>948</v>
+        <v>1103</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="2">
-        <v>46283.19791666666</v>
+        <v>46285.19791666666</v>
       </c>
       <c r="B21">
-        <v>533</v>
+        <v>590</v>
       </c>
       <c r="C21">
-        <v>425</v>
+        <v>515</v>
       </c>
       <c r="D21">
-        <v>1430.26149336219</v>
+        <v>1252.600850018373</v>
       </c>
       <c r="E21">
-        <v>958</v>
+        <v>1105</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="2">
-        <v>46283.20833333334</v>
+        <v>46285.20833333334</v>
       </c>
       <c r="B22">
-        <v>705</v>
+        <v>437</v>
       </c>
       <c r="C22">
-        <v>449</v>
+        <v>475</v>
       </c>
       <c r="D22">
-        <v>1442.528519777175</v>
+        <v>1273.659401669024</v>
       </c>
       <c r="E22">
-        <v>1154</v>
+        <v>912</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="2">
-        <v>46283.21875</v>
+        <v>46285.21875</v>
       </c>
       <c r="B23">
-        <v>726</v>
+        <v>435</v>
       </c>
       <c r="C23">
-        <v>461</v>
+        <v>471</v>
       </c>
       <c r="D23">
-        <v>1479.780517286268</v>
+        <v>1310.663564228931</v>
       </c>
       <c r="E23">
-        <v>1187</v>
+        <v>906</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="2">
-        <v>46283.22916666666</v>
+        <v>46285.22916666666</v>
       </c>
       <c r="B24">
-        <v>723</v>
+        <v>432</v>
       </c>
       <c r="C24">
-        <v>556</v>
+        <v>471</v>
       </c>
       <c r="D24">
-        <v>1517.032514795362</v>
+        <v>1347.667726788837</v>
       </c>
       <c r="E24">
-        <v>1279</v>
+        <v>903</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="2">
-        <v>46283.23958333334</v>
+        <v>46285.23958333334</v>
       </c>
       <c r="B25">
-        <v>737</v>
+        <v>436</v>
       </c>
       <c r="C25">
-        <v>551</v>
+        <v>471</v>
       </c>
       <c r="D25">
-        <v>1554.284512304456</v>
+        <v>1384.671889348744</v>
       </c>
       <c r="E25">
-        <v>1288</v>
+        <v>907</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="2">
-        <v>46283.25</v>
+        <v>46285.25</v>
       </c>
       <c r="B26">
-        <v>773</v>
+        <v>608</v>
       </c>
       <c r="C26">
-        <v>663</v>
+        <v>512</v>
       </c>
       <c r="D26">
-        <v>1591.53650981355</v>
+        <v>1421.67605190865</v>
       </c>
       <c r="E26">
-        <v>1436</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="2">
-        <v>46283.26041666666</v>
+        <v>46285.26041666666</v>
       </c>
       <c r="B27">
-        <v>777</v>
+        <v>620</v>
       </c>
       <c r="C27">
-        <v>667</v>
+        <v>513</v>
       </c>
       <c r="D27">
-        <v>1595.461548340578</v>
+        <v>1420.890210822022</v>
       </c>
       <c r="E27">
-        <v>1444</v>
+        <v>1133</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="2">
-        <v>46283.27083333334</v>
+        <v>46285.27083333334</v>
       </c>
       <c r="B28">
-        <v>772</v>
+        <v>632</v>
       </c>
       <c r="C28">
-        <v>666</v>
+        <v>513</v>
       </c>
       <c r="D28">
-        <v>1599.386586867606</v>
+        <v>1420.104369735395</v>
       </c>
       <c r="E28">
-        <v>1438</v>
+        <v>1145</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="2">
-        <v>46283.28125</v>
+        <v>46285.28125</v>
       </c>
       <c r="B29">
-        <v>761</v>
+        <v>620</v>
       </c>
       <c r="C29">
-        <v>666</v>
+        <v>511</v>
       </c>
       <c r="D29">
-        <v>1603.311625394634</v>
+        <v>1419.318528648768</v>
       </c>
       <c r="E29">
-        <v>1427</v>
+        <v>1131</v>
       </c>
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="2">
-        <v>46283.29166666666</v>
+        <v>46285.29166666666</v>
       </c>
       <c r="B30">
-        <v>805</v>
+        <v>117</v>
       </c>
       <c r="C30">
-        <v>665</v>
+        <v>276</v>
       </c>
       <c r="D30">
-        <v>1607.236663921662</v>
+        <v>1418.53268756214</v>
       </c>
       <c r="E30">
-        <v>1470</v>
+        <v>393</v>
       </c>
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="2">
-        <v>46283.30208333334</v>
+        <v>46285.30208333334</v>
       </c>
       <c r="B31">
-        <v>829</v>
+        <v>97</v>
       </c>
       <c r="C31">
-        <v>648</v>
+        <v>254</v>
       </c>
       <c r="D31">
-        <v>1565.291017207909</v>
+        <v>1349.458250783268</v>
       </c>
       <c r="E31">
-        <v>1477</v>
+        <v>351</v>
       </c>
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="2">
-        <v>46283.3125</v>
+        <v>46285.3125</v>
       </c>
       <c r="B32">
-        <v>829</v>
+        <v>89</v>
       </c>
       <c r="C32">
-        <v>648</v>
+        <v>254</v>
       </c>
       <c r="D32">
-        <v>1523.345370494157</v>
+        <v>1280.383814004395</v>
       </c>
       <c r="E32">
-        <v>1477</v>
+        <v>343</v>
       </c>
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="2">
-        <v>46283.32291666666</v>
+        <v>46285.32291666666</v>
       </c>
       <c r="B33">
-        <v>829</v>
+        <v>86</v>
       </c>
       <c r="C33">
-        <v>648</v>
+        <v>254</v>
       </c>
       <c r="D33">
-        <v>1481.399723780405</v>
+        <v>1211.309377225523</v>
       </c>
       <c r="E33">
-        <v>1477</v>
+        <v>340</v>
       </c>
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="2">
-        <v>46283.33333333334</v>
+        <v>46285.33333333334</v>
       </c>
       <c r="B34">
-        <v>829</v>
+        <v>74</v>
       </c>
       <c r="C34">
-        <v>648</v>
+        <v>246</v>
       </c>
       <c r="D34">
-        <v>1439.454077066652</v>
+        <v>1142.23494044665</v>
       </c>
       <c r="E34">
-        <v>1477</v>
+        <v>320</v>
       </c>
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="2">
-        <v>46283.34375</v>
+        <v>46285.34375</v>
       </c>
       <c r="B35">
-        <v>829</v>
+        <v>73</v>
       </c>
       <c r="C35">
-        <v>648</v>
+        <v>244</v>
       </c>
       <c r="D35">
-        <v>1278.240549469183</v>
+        <v>992.8654498541971</v>
       </c>
       <c r="E35">
-        <v>1477</v>
+        <v>317</v>
       </c>
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="2">
-        <v>46283.35416666666</v>
+        <v>46285.35416666666</v>
       </c>
       <c r="B36">
-        <v>102</v>
+        <v>72</v>
       </c>
       <c r="C36">
-        <v>522</v>
+        <v>244</v>
       </c>
       <c r="D36">
-        <v>1117.027021871714</v>
+        <v>843.4959592617441</v>
       </c>
       <c r="E36">
-        <v>624</v>
+        <v>316</v>
       </c>
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="2">
-        <v>46283.36458333334</v>
+        <v>46285.36458333334</v>
       </c>
       <c r="B37">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="C37">
-        <v>519</v>
+        <v>245</v>
       </c>
       <c r="D37">
-        <v>955.8134942742454</v>
+        <v>694.1264686692912</v>
       </c>
       <c r="E37">
-        <v>596</v>
+        <v>316</v>
       </c>
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="2">
-        <v>46283.375</v>
+        <v>46285.375</v>
       </c>
       <c r="B38">
-        <v>61</v>
+        <v>88</v>
       </c>
       <c r="C38">
-        <v>332</v>
+        <v>241</v>
       </c>
       <c r="D38">
-        <v>794.5999666767764</v>
+        <v>544.7569780768381</v>
       </c>
       <c r="E38">
-        <v>393</v>
+        <v>329</v>
       </c>
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="2">
-        <v>46283.38541666666</v>
+        <v>46285.38541666666</v>
       </c>
       <c r="B39">
-        <v>60</v>
+        <v>86</v>
       </c>
       <c r="C39">
-        <v>306</v>
+        <v>239</v>
       </c>
       <c r="D39">
-        <v>729.8317069084943</v>
+        <v>498.4818801655939</v>
       </c>
       <c r="E39">
-        <v>366</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
-      <c r="A40" s="2">
-        <v>46283.39583333334</v>
-      </c>
-      <c r="B40">
-        <v>59</v>
-      </c>
-      <c r="C40">
-        <v>305</v>
-      </c>
-      <c r="D40">
-        <v>665.0634471402122</v>
-      </c>
-      <c r="E40">
-        <v>364</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
-      <c r="A41" s="2">
-        <v>46283.40625</v>
-      </c>
-      <c r="B41">
-        <v>58</v>
-      </c>
-      <c r="C41">
-        <v>304</v>
-      </c>
-      <c r="D41">
-        <v>600.2951873719301</v>
-      </c>
-      <c r="E41">
-        <v>362</v>
+        <v>325</v>
       </c>
     </row>
   </sheetData>

--- a/data_fetching/Entsoe/Hydro_Production.xlsx
+++ b/data_fetching/Entsoe/Hydro_Production.xlsx
@@ -390,7 +390,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E39"/>
+  <dimension ref="A1:E40"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:5">
@@ -412,648 +412,665 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="2">
-        <v>46285</v>
+        <v>46295</v>
       </c>
       <c r="B2">
-        <v>560</v>
+        <v>38</v>
       </c>
       <c r="C2">
-        <v>616</v>
+        <v>229</v>
       </c>
       <c r="D2">
-        <v>1239.957761143239</v>
+        <v>763.8081954184732</v>
       </c>
       <c r="E2">
-        <v>1176</v>
+        <v>267</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="2">
-        <v>46285.01041666666</v>
+        <v>46295.01041666666</v>
       </c>
       <c r="B3">
-        <v>566</v>
+        <v>40</v>
       </c>
       <c r="C3">
-        <v>616</v>
+        <v>231</v>
       </c>
       <c r="D3">
-        <v>1206.843014594079</v>
+        <v>754.3118990953662</v>
       </c>
       <c r="E3">
-        <v>1182</v>
+        <v>271</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="2">
-        <v>46285.02083333334</v>
+        <v>46295.02083333334</v>
       </c>
       <c r="B4">
-        <v>566</v>
+        <v>39</v>
       </c>
       <c r="C4">
-        <v>617</v>
+        <v>230</v>
       </c>
       <c r="D4">
-        <v>1173.72826804492</v>
+        <v>744.8156027722591</v>
       </c>
       <c r="E4">
-        <v>1183</v>
+        <v>269</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="2">
-        <v>46285.03125</v>
+        <v>46295.03125</v>
       </c>
       <c r="B5">
-        <v>582</v>
+        <v>38</v>
       </c>
       <c r="C5">
-        <v>617</v>
+        <v>229</v>
       </c>
       <c r="D5">
-        <v>1140.61352149576</v>
+        <v>735.319306449152</v>
       </c>
       <c r="E5">
-        <v>1199</v>
+        <v>267</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="2">
-        <v>46285.04166666666</v>
+        <v>46295.04166666666</v>
       </c>
       <c r="B6">
-        <v>655</v>
+        <v>38</v>
       </c>
       <c r="C6">
-        <v>518</v>
+        <v>227</v>
       </c>
       <c r="D6">
-        <v>1107.4987749466</v>
+        <v>725.823010126045</v>
       </c>
       <c r="E6">
-        <v>1173</v>
+        <v>265</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="2">
-        <v>46285.05208333334</v>
+        <v>46295.05208333334</v>
       </c>
       <c r="B7">
-        <v>655</v>
+        <v>39</v>
       </c>
       <c r="C7">
-        <v>503</v>
+        <v>227</v>
       </c>
       <c r="D7">
-        <v>1114.004345461215</v>
+        <v>723.4162866964167</v>
       </c>
       <c r="E7">
-        <v>1158</v>
+        <v>266</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="2">
-        <v>46285.0625</v>
+        <v>46295.0625</v>
       </c>
       <c r="B8">
-        <v>655</v>
+        <v>39</v>
       </c>
       <c r="C8">
-        <v>502</v>
+        <v>227</v>
       </c>
       <c r="D8">
-        <v>1120.509915975829</v>
+        <v>721.0095632667884</v>
       </c>
       <c r="E8">
-        <v>1157</v>
+        <v>266</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="2">
-        <v>46285.07291666666</v>
+        <v>46295.07291666666</v>
       </c>
       <c r="B9">
-        <v>655</v>
+        <v>38</v>
       </c>
       <c r="C9">
-        <v>502</v>
+        <v>227</v>
       </c>
       <c r="D9">
-        <v>1127.015486490443</v>
+        <v>718.6028398371601</v>
       </c>
       <c r="E9">
-        <v>1157</v>
+        <v>265</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="2">
-        <v>46285.08333333334</v>
+        <v>46295.08333333334</v>
       </c>
       <c r="B10">
-        <v>606</v>
+        <v>39</v>
       </c>
       <c r="C10">
-        <v>502</v>
+        <v>220</v>
       </c>
       <c r="D10">
-        <v>1133.521057005057</v>
+        <v>716.1961164075318</v>
       </c>
       <c r="E10">
-        <v>1108</v>
+        <v>259</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="2">
-        <v>46285.09375</v>
+        <v>46295.09375</v>
       </c>
       <c r="B11">
-        <v>606</v>
+        <v>38</v>
       </c>
       <c r="C11">
-        <v>502</v>
+        <v>219</v>
       </c>
       <c r="D11">
-        <v>1111.875611378341</v>
+        <v>711.7837901198799</v>
       </c>
       <c r="E11">
-        <v>1108</v>
+        <v>257</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="2">
-        <v>46285.10416666666</v>
+        <v>46295.10416666666</v>
       </c>
       <c r="B12">
-        <v>606</v>
+        <v>39</v>
       </c>
       <c r="C12">
-        <v>502</v>
+        <v>219</v>
       </c>
       <c r="D12">
-        <v>1090.230165751624</v>
+        <v>707.371463832228</v>
       </c>
       <c r="E12">
-        <v>1108</v>
+        <v>258</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="2">
-        <v>46285.11458333334</v>
+        <v>46295.11458333334</v>
       </c>
       <c r="B13">
-        <v>606</v>
+        <v>39</v>
       </c>
       <c r="C13">
-        <v>502</v>
+        <v>219</v>
       </c>
       <c r="D13">
-        <v>1068.584720124908</v>
+        <v>702.959137544576</v>
       </c>
       <c r="E13">
-        <v>1108</v>
+        <v>258</v>
       </c>
     </row>
     <row r="14" spans="1:5">
       <c r="A14" s="2">
-        <v>46285.125</v>
+        <v>46295.125</v>
       </c>
       <c r="B14">
-        <v>607</v>
+        <v>38</v>
       </c>
       <c r="C14">
-        <v>502</v>
+        <v>224</v>
       </c>
       <c r="D14">
-        <v>1046.939274498192</v>
+        <v>698.5468112569241</v>
       </c>
       <c r="E14">
-        <v>1109</v>
+        <v>262</v>
       </c>
     </row>
     <row r="15" spans="1:5">
       <c r="A15" s="2">
-        <v>46285.13541666666</v>
+        <v>46295.13541666666</v>
       </c>
       <c r="B15">
-        <v>606</v>
+        <v>37</v>
       </c>
       <c r="C15">
-        <v>501</v>
+        <v>224</v>
       </c>
       <c r="D15">
-        <v>1082.560754640249</v>
+        <v>698.8359912039409</v>
       </c>
       <c r="E15">
-        <v>1107</v>
+        <v>261</v>
       </c>
     </row>
     <row r="16" spans="1:5">
       <c r="A16" s="2">
-        <v>46285.14583333334</v>
+        <v>46295.14583333334</v>
       </c>
       <c r="B16">
-        <v>607</v>
+        <v>38</v>
       </c>
       <c r="C16">
-        <v>502</v>
+        <v>224</v>
       </c>
       <c r="D16">
-        <v>1118.182234782306</v>
+        <v>699.1251711509578</v>
       </c>
       <c r="E16">
-        <v>1109</v>
+        <v>262</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="2">
-        <v>46285.15625</v>
+        <v>46295.15625</v>
       </c>
       <c r="B17">
-        <v>606</v>
+        <v>38</v>
       </c>
       <c r="C17">
-        <v>501</v>
+        <v>224</v>
       </c>
       <c r="D17">
-        <v>1153.803714924363</v>
+        <v>699.4143510979746</v>
       </c>
       <c r="E17">
-        <v>1107</v>
+        <v>262</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="2">
-        <v>46285.16666666666</v>
+        <v>46295.16666666666</v>
       </c>
       <c r="B18">
-        <v>589</v>
+        <v>39</v>
       </c>
       <c r="C18">
-        <v>510</v>
+        <v>225</v>
       </c>
       <c r="D18">
-        <v>1189.42519506642</v>
+        <v>699.7035310449915</v>
       </c>
       <c r="E18">
-        <v>1099</v>
+        <v>264</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="2">
-        <v>46285.17708333334</v>
+        <v>46295.17708333334</v>
       </c>
       <c r="B19">
-        <v>588</v>
+        <v>39</v>
       </c>
       <c r="C19">
-        <v>515</v>
+        <v>244</v>
       </c>
       <c r="D19">
-        <v>1210.483746717071</v>
+        <v>722.959195812685</v>
       </c>
       <c r="E19">
-        <v>1103</v>
+        <v>283</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="2">
-        <v>46285.1875</v>
+        <v>46295.1875</v>
       </c>
       <c r="B20">
-        <v>588</v>
+        <v>39</v>
       </c>
       <c r="C20">
-        <v>515</v>
+        <v>245</v>
       </c>
       <c r="D20">
-        <v>1231.542298367722</v>
+        <v>746.2148605803787</v>
       </c>
       <c r="E20">
-        <v>1103</v>
+        <v>284</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="2">
-        <v>46285.19791666666</v>
+        <v>46295.19791666666</v>
       </c>
       <c r="B21">
-        <v>590</v>
+        <v>44</v>
       </c>
       <c r="C21">
-        <v>515</v>
+        <v>246</v>
       </c>
       <c r="D21">
-        <v>1252.600850018373</v>
+        <v>769.4705253480724</v>
       </c>
       <c r="E21">
-        <v>1105</v>
+        <v>290</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="2">
-        <v>46285.20833333334</v>
+        <v>46295.20833333334</v>
       </c>
       <c r="B22">
-        <v>437</v>
+        <v>91</v>
       </c>
       <c r="C22">
-        <v>475</v>
+        <v>297</v>
       </c>
       <c r="D22">
-        <v>1273.659401669024</v>
+        <v>792.726190115766</v>
       </c>
       <c r="E22">
-        <v>912</v>
+        <v>388</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="2">
-        <v>46285.21875</v>
+        <v>46295.21875</v>
       </c>
       <c r="B23">
-        <v>435</v>
+        <v>94</v>
       </c>
       <c r="C23">
-        <v>471</v>
+        <v>297</v>
       </c>
       <c r="D23">
-        <v>1310.663564228931</v>
+        <v>899.8253827343342</v>
       </c>
       <c r="E23">
-        <v>906</v>
+        <v>391</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="2">
-        <v>46285.22916666666</v>
+        <v>46295.22916666666</v>
       </c>
       <c r="B24">
-        <v>432</v>
+        <v>96</v>
       </c>
       <c r="C24">
-        <v>471</v>
+        <v>298</v>
       </c>
       <c r="D24">
-        <v>1347.667726788837</v>
+        <v>1006.924575352902</v>
       </c>
       <c r="E24">
-        <v>903</v>
+        <v>394</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="2">
-        <v>46285.23958333334</v>
+        <v>46295.23958333334</v>
       </c>
       <c r="B25">
-        <v>436</v>
+        <v>115</v>
       </c>
       <c r="C25">
-        <v>471</v>
+        <v>302</v>
       </c>
       <c r="D25">
-        <v>1384.671889348744</v>
+        <v>1114.023767971471</v>
       </c>
       <c r="E25">
-        <v>907</v>
+        <v>417</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="2">
-        <v>46285.25</v>
+        <v>46295.25</v>
       </c>
       <c r="B26">
-        <v>608</v>
+        <v>165</v>
       </c>
       <c r="C26">
-        <v>512</v>
+        <v>600</v>
       </c>
       <c r="D26">
-        <v>1421.67605190865</v>
+        <v>1221.122960590039</v>
       </c>
       <c r="E26">
-        <v>1120</v>
+        <v>765</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="2">
-        <v>46285.26041666666</v>
+        <v>46295.26041666666</v>
       </c>
       <c r="B27">
-        <v>620</v>
+        <v>160</v>
       </c>
       <c r="C27">
-        <v>513</v>
+        <v>649</v>
       </c>
       <c r="D27">
-        <v>1420.890210822022</v>
+        <v>1228.483056659474</v>
       </c>
       <c r="E27">
-        <v>1133</v>
+        <v>809</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="2">
-        <v>46285.27083333334</v>
+        <v>46295.27083333334</v>
       </c>
       <c r="B28">
-        <v>632</v>
+        <v>158</v>
       </c>
       <c r="C28">
-        <v>513</v>
+        <v>643</v>
       </c>
       <c r="D28">
-        <v>1420.104369735395</v>
+        <v>1235.843152728908</v>
       </c>
       <c r="E28">
-        <v>1145</v>
+        <v>801</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="2">
-        <v>46285.28125</v>
+        <v>46295.28125</v>
       </c>
       <c r="B29">
-        <v>620</v>
+        <v>158</v>
       </c>
       <c r="C29">
-        <v>511</v>
+        <v>645</v>
       </c>
       <c r="D29">
-        <v>1419.318528648768</v>
+        <v>1243.203248798343</v>
       </c>
       <c r="E29">
-        <v>1131</v>
+        <v>803</v>
       </c>
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="2">
-        <v>46285.29166666666</v>
+        <v>46295.29166666666</v>
       </c>
       <c r="B30">
-        <v>117</v>
+        <v>153</v>
       </c>
       <c r="C30">
-        <v>276</v>
+        <v>623</v>
       </c>
       <c r="D30">
-        <v>1418.53268756214</v>
+        <v>1250.563344867777</v>
       </c>
       <c r="E30">
-        <v>393</v>
+        <v>776</v>
       </c>
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="2">
-        <v>46285.30208333334</v>
+        <v>46295.30208333334</v>
       </c>
       <c r="B31">
-        <v>97</v>
+        <v>177</v>
       </c>
       <c r="C31">
-        <v>254</v>
+        <v>636</v>
       </c>
       <c r="D31">
-        <v>1349.458250783268</v>
+        <v>1169.686243570007</v>
       </c>
       <c r="E31">
-        <v>351</v>
+        <v>813</v>
       </c>
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="2">
-        <v>46285.3125</v>
+        <v>46295.3125</v>
       </c>
       <c r="B32">
-        <v>89</v>
+        <v>279</v>
       </c>
       <c r="C32">
-        <v>254</v>
+        <v>638</v>
       </c>
       <c r="D32">
-        <v>1280.383814004395</v>
+        <v>1088.809142272236</v>
       </c>
       <c r="E32">
-        <v>343</v>
+        <v>917</v>
       </c>
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="2">
-        <v>46285.32291666666</v>
+        <v>46295.32291666666</v>
       </c>
       <c r="B33">
-        <v>86</v>
+        <v>303</v>
       </c>
       <c r="C33">
-        <v>254</v>
+        <v>637</v>
       </c>
       <c r="D33">
-        <v>1211.309377225523</v>
+        <v>1007.932040974466</v>
       </c>
       <c r="E33">
-        <v>340</v>
+        <v>940</v>
       </c>
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="2">
-        <v>46285.33333333334</v>
+        <v>46295.33333333334</v>
       </c>
       <c r="B34">
-        <v>74</v>
+        <v>377</v>
       </c>
       <c r="C34">
-        <v>246</v>
+        <v>461</v>
       </c>
       <c r="D34">
-        <v>1142.23494044665</v>
+        <v>927.054939676695</v>
       </c>
       <c r="E34">
-        <v>320</v>
+        <v>838</v>
       </c>
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="2">
-        <v>46285.34375</v>
+        <v>46295.34375</v>
       </c>
       <c r="B35">
-        <v>73</v>
+        <v>394</v>
       </c>
       <c r="C35">
-        <v>244</v>
+        <v>418</v>
       </c>
       <c r="D35">
-        <v>992.8654498541971</v>
+        <v>879.3682335825424</v>
       </c>
       <c r="E35">
-        <v>317</v>
+        <v>812</v>
       </c>
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="2">
-        <v>46285.35416666666</v>
+        <v>46295.35416666666</v>
       </c>
       <c r="B36">
-        <v>72</v>
+        <v>398</v>
       </c>
       <c r="C36">
-        <v>244</v>
+        <v>420</v>
       </c>
       <c r="D36">
-        <v>843.4959592617441</v>
+        <v>831.6815274883897</v>
       </c>
       <c r="E36">
-        <v>316</v>
+        <v>818</v>
       </c>
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="2">
-        <v>46285.36458333334</v>
+        <v>46295.36458333334</v>
       </c>
       <c r="B37">
-        <v>71</v>
+        <v>362</v>
       </c>
       <c r="C37">
-        <v>245</v>
+        <v>417</v>
       </c>
       <c r="D37">
-        <v>694.1264686692912</v>
+        <v>783.9948213942372</v>
       </c>
       <c r="E37">
-        <v>316</v>
+        <v>779</v>
       </c>
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="2">
-        <v>46285.375</v>
+        <v>46295.375</v>
       </c>
       <c r="B38">
-        <v>88</v>
+        <v>390</v>
       </c>
       <c r="C38">
-        <v>241</v>
+        <v>319</v>
       </c>
       <c r="D38">
-        <v>544.7569780768381</v>
+        <v>736.3081153000846</v>
       </c>
       <c r="E38">
-        <v>329</v>
+        <v>709</v>
       </c>
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="2">
-        <v>46285.38541666666</v>
+        <v>46295.38541666666</v>
       </c>
       <c r="B39">
-        <v>86</v>
+        <v>400</v>
       </c>
       <c r="C39">
-        <v>239</v>
+        <v>310</v>
       </c>
       <c r="D39">
-        <v>498.4818801655939</v>
+        <v>663.5746944442536</v>
       </c>
       <c r="E39">
-        <v>325</v>
+        <v>710</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="2">
+        <v>46295.39583333334</v>
+      </c>
+      <c r="B40">
+        <v>401</v>
+      </c>
+      <c r="C40">
+        <v>313</v>
+      </c>
+      <c r="D40">
+        <v>590.8412735884227</v>
+      </c>
+      <c r="E40">
+        <v>714</v>
       </c>
     </row>
   </sheetData>

--- a/data_fetching/Entsoe/Hydro_Production.xlsx
+++ b/data_fetching/Entsoe/Hydro_Production.xlsx
@@ -35,6 +35,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <sz val="11"/>
@@ -87,11 +90,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -386,7 +390,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E1"/>
+  <dimension ref="A1:E40"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:5">
@@ -406,6 +410,669 @@
         <v>4</v>
       </c>
     </row>
+    <row r="2" spans="1:5">
+      <c r="A2" s="2">
+        <v>46307</v>
+      </c>
+      <c r="B2">
+        <v>322</v>
+      </c>
+      <c r="C2">
+        <v>304</v>
+      </c>
+      <c r="D2">
+        <v>901.0759710952658</v>
+      </c>
+      <c r="E2">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3" s="2">
+        <v>46307.01041666666</v>
+      </c>
+      <c r="B3">
+        <v>318</v>
+      </c>
+      <c r="C3">
+        <v>307</v>
+      </c>
+      <c r="D3">
+        <v>909.4156893812033</v>
+      </c>
+      <c r="E3">
+        <v>625</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" s="2">
+        <v>46307.02083333334</v>
+      </c>
+      <c r="B4">
+        <v>318</v>
+      </c>
+      <c r="C4">
+        <v>341</v>
+      </c>
+      <c r="D4">
+        <v>917.7554076671407</v>
+      </c>
+      <c r="E4">
+        <v>659</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" s="2">
+        <v>46307.03125</v>
+      </c>
+      <c r="B5">
+        <v>322</v>
+      </c>
+      <c r="C5">
+        <v>341</v>
+      </c>
+      <c r="D5">
+        <v>926.0951259530782</v>
+      </c>
+      <c r="E5">
+        <v>663</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6" s="2">
+        <v>46307.04166666666</v>
+      </c>
+      <c r="B6">
+        <v>400</v>
+      </c>
+      <c r="C6">
+        <v>339</v>
+      </c>
+      <c r="D6">
+        <v>934.4348442390157</v>
+      </c>
+      <c r="E6">
+        <v>739</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7" s="2">
+        <v>46307.05208333334</v>
+      </c>
+      <c r="B7">
+        <v>390</v>
+      </c>
+      <c r="C7">
+        <v>309</v>
+      </c>
+      <c r="D7">
+        <v>919.2365931542184</v>
+      </c>
+      <c r="E7">
+        <v>699</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="A8" s="2">
+        <v>46307.0625</v>
+      </c>
+      <c r="B8">
+        <v>390</v>
+      </c>
+      <c r="C8">
+        <v>340</v>
+      </c>
+      <c r="D8">
+        <v>904.0383420694212</v>
+      </c>
+      <c r="E8">
+        <v>730</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="A9" s="2">
+        <v>46307.07291666666</v>
+      </c>
+      <c r="B9">
+        <v>390</v>
+      </c>
+      <c r="C9">
+        <v>323</v>
+      </c>
+      <c r="D9">
+        <v>888.840090984624</v>
+      </c>
+      <c r="E9">
+        <v>713</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="A10" s="2">
+        <v>46307.08333333334</v>
+      </c>
+      <c r="B10">
+        <v>405</v>
+      </c>
+      <c r="C10">
+        <v>337</v>
+      </c>
+      <c r="D10">
+        <v>873.6418398998268</v>
+      </c>
+      <c r="E10">
+        <v>742</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5">
+      <c r="A11" s="2">
+        <v>46307.09375</v>
+      </c>
+      <c r="B11">
+        <v>405</v>
+      </c>
+      <c r="C11">
+        <v>327</v>
+      </c>
+      <c r="D11">
+        <v>846.9697679042205</v>
+      </c>
+      <c r="E11">
+        <v>732</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5">
+      <c r="A12" s="2">
+        <v>46307.10416666666</v>
+      </c>
+      <c r="B12">
+        <v>406</v>
+      </c>
+      <c r="C12">
+        <v>329</v>
+      </c>
+      <c r="D12">
+        <v>820.2976959086142</v>
+      </c>
+      <c r="E12">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5">
+      <c r="A13" s="2">
+        <v>46307.11458333334</v>
+      </c>
+      <c r="B13">
+        <v>357</v>
+      </c>
+      <c r="C13">
+        <v>327</v>
+      </c>
+      <c r="D13">
+        <v>793.6256239130079</v>
+      </c>
+      <c r="E13">
+        <v>684</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5">
+      <c r="A14" s="2">
+        <v>46307.125</v>
+      </c>
+      <c r="B14">
+        <v>286</v>
+      </c>
+      <c r="C14">
+        <v>308</v>
+      </c>
+      <c r="D14">
+        <v>766.9535519174016</v>
+      </c>
+      <c r="E14">
+        <v>594</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5">
+      <c r="A15" s="2">
+        <v>46307.13541666666</v>
+      </c>
+      <c r="B15">
+        <v>282</v>
+      </c>
+      <c r="C15">
+        <v>303</v>
+      </c>
+      <c r="D15">
+        <v>795.718603405571</v>
+      </c>
+      <c r="E15">
+        <v>585</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5">
+      <c r="A16" s="2">
+        <v>46307.14583333334</v>
+      </c>
+      <c r="B16">
+        <v>255</v>
+      </c>
+      <c r="C16">
+        <v>304</v>
+      </c>
+      <c r="D16">
+        <v>824.4836548937404</v>
+      </c>
+      <c r="E16">
+        <v>559</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="2">
+        <v>46307.15625</v>
+      </c>
+      <c r="B17">
+        <v>250</v>
+      </c>
+      <c r="C17">
+        <v>304</v>
+      </c>
+      <c r="D17">
+        <v>853.2487063819099</v>
+      </c>
+      <c r="E17">
+        <v>554</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="2">
+        <v>46307.16666666666</v>
+      </c>
+      <c r="B18">
+        <v>114</v>
+      </c>
+      <c r="C18">
+        <v>258</v>
+      </c>
+      <c r="D18">
+        <v>882.0137578700793</v>
+      </c>
+      <c r="E18">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="2">
+        <v>46307.17708333334</v>
+      </c>
+      <c r="B19">
+        <v>81</v>
+      </c>
+      <c r="C19">
+        <v>261</v>
+      </c>
+      <c r="D19">
+        <v>988.0258524778535</v>
+      </c>
+      <c r="E19">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="2">
+        <v>46307.1875</v>
+      </c>
+      <c r="B20">
+        <v>80</v>
+      </c>
+      <c r="C20">
+        <v>265</v>
+      </c>
+      <c r="D20">
+        <v>1094.037947085628</v>
+      </c>
+      <c r="E20">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="2">
+        <v>46307.19791666666</v>
+      </c>
+      <c r="B21">
+        <v>91</v>
+      </c>
+      <c r="C21">
+        <v>266</v>
+      </c>
+      <c r="D21">
+        <v>1200.050041693402</v>
+      </c>
+      <c r="E21">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="2">
+        <v>46307.20833333334</v>
+      </c>
+      <c r="B22">
+        <v>336</v>
+      </c>
+      <c r="C22">
+        <v>378</v>
+      </c>
+      <c r="D22">
+        <v>1306.062136301176</v>
+      </c>
+      <c r="E22">
+        <v>714</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="2">
+        <v>46307.21875</v>
+      </c>
+      <c r="B23">
+        <v>356</v>
+      </c>
+      <c r="C23">
+        <v>390</v>
+      </c>
+      <c r="D23">
+        <v>1388.17133178031</v>
+      </c>
+      <c r="E23">
+        <v>746</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="2">
+        <v>46307.22916666666</v>
+      </c>
+      <c r="B24">
+        <v>357</v>
+      </c>
+      <c r="C24">
+        <v>403</v>
+      </c>
+      <c r="D24">
+        <v>1470.280527259444</v>
+      </c>
+      <c r="E24">
+        <v>760</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="2">
+        <v>46307.23958333334</v>
+      </c>
+      <c r="B25">
+        <v>386</v>
+      </c>
+      <c r="C25">
+        <v>412</v>
+      </c>
+      <c r="D25">
+        <v>1552.389722738579</v>
+      </c>
+      <c r="E25">
+        <v>798</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="2">
+        <v>46307.25</v>
+      </c>
+      <c r="B26">
+        <v>553</v>
+      </c>
+      <c r="C26">
+        <v>451</v>
+      </c>
+      <c r="D26">
+        <v>1634.498918217713</v>
+      </c>
+      <c r="E26">
+        <v>1004</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="2">
+        <v>46307.26041666666</v>
+      </c>
+      <c r="B27">
+        <v>654</v>
+      </c>
+      <c r="C27">
+        <v>459</v>
+      </c>
+      <c r="D27">
+        <v>1642.945968785584</v>
+      </c>
+      <c r="E27">
+        <v>1113</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="2">
+        <v>46307.27083333334</v>
+      </c>
+      <c r="B28">
+        <v>829</v>
+      </c>
+      <c r="C28">
+        <v>478</v>
+      </c>
+      <c r="D28">
+        <v>1651.393019353454</v>
+      </c>
+      <c r="E28">
+        <v>1307</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="2">
+        <v>46307.28125</v>
+      </c>
+      <c r="B29">
+        <v>917</v>
+      </c>
+      <c r="C29">
+        <v>480</v>
+      </c>
+      <c r="D29">
+        <v>1659.840069921325</v>
+      </c>
+      <c r="E29">
+        <v>1397</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="2">
+        <v>46307.29166666666</v>
+      </c>
+      <c r="B30">
+        <v>956</v>
+      </c>
+      <c r="C30">
+        <v>468</v>
+      </c>
+      <c r="D30">
+        <v>1668.287120489196</v>
+      </c>
+      <c r="E30">
+        <v>1424</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="2">
+        <v>46307.30208333334</v>
+      </c>
+      <c r="B31">
+        <v>986</v>
+      </c>
+      <c r="C31">
+        <v>514</v>
+      </c>
+      <c r="D31">
+        <v>1607.011120882393</v>
+      </c>
+      <c r="E31">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="2">
+        <v>46307.3125</v>
+      </c>
+      <c r="B32">
+        <v>1100</v>
+      </c>
+      <c r="C32">
+        <v>674</v>
+      </c>
+      <c r="D32">
+        <v>1545.735121275591</v>
+      </c>
+      <c r="E32">
+        <v>1774</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="2">
+        <v>46307.32291666666</v>
+      </c>
+      <c r="B33">
+        <v>1108</v>
+      </c>
+      <c r="C33">
+        <v>678</v>
+      </c>
+      <c r="D33">
+        <v>1484.459121668789</v>
+      </c>
+      <c r="E33">
+        <v>1786</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="2">
+        <v>46307.33333333334</v>
+      </c>
+      <c r="B34">
+        <v>1273</v>
+      </c>
+      <c r="C34">
+        <v>646</v>
+      </c>
+      <c r="D34">
+        <v>1423.183122061986</v>
+      </c>
+      <c r="E34">
+        <v>1919</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="2">
+        <v>46307.34375</v>
+      </c>
+      <c r="B35">
+        <v>1218</v>
+      </c>
+      <c r="C35">
+        <v>650</v>
+      </c>
+      <c r="D35">
+        <v>1204.278933591308</v>
+      </c>
+      <c r="E35">
+        <v>1868</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="2">
+        <v>46307.35416666666</v>
+      </c>
+      <c r="B36">
+        <v>1141</v>
+      </c>
+      <c r="C36">
+        <v>634</v>
+      </c>
+      <c r="D36">
+        <v>985.3747451206298</v>
+      </c>
+      <c r="E36">
+        <v>1775</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="2">
+        <v>46307.36458333334</v>
+      </c>
+      <c r="B37">
+        <v>1122</v>
+      </c>
+      <c r="C37">
+        <v>638</v>
+      </c>
+      <c r="D37">
+        <v>766.4705566499516</v>
+      </c>
+      <c r="E37">
+        <v>1760</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="2">
+        <v>46307.375</v>
+      </c>
+      <c r="B38">
+        <v>1050</v>
+      </c>
+      <c r="C38">
+        <v>462</v>
+      </c>
+      <c r="D38">
+        <v>547.5663681792735</v>
+      </c>
+      <c r="E38">
+        <v>1512</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="2">
+        <v>46307.38541666666</v>
+      </c>
+      <c r="B39">
+        <v>1003</v>
+      </c>
+      <c r="C39">
+        <v>440</v>
+      </c>
+      <c r="D39">
+        <v>498.5155154550628</v>
+      </c>
+      <c r="E39">
+        <v>1443</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="2">
+        <v>46307.39583333334</v>
+      </c>
+      <c r="B40">
+        <v>1076</v>
+      </c>
+      <c r="C40">
+        <v>438</v>
+      </c>
+      <c r="D40">
+        <v>449.4646627308521</v>
+      </c>
+      <c r="E40">
+        <v>1514</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data_fetching/Entsoe/Hydro_Production.xlsx
+++ b/data_fetching/Entsoe/Hydro_Production.xlsx
@@ -390,7 +390,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E40"/>
+  <dimension ref="A1:E56"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:5">
@@ -412,665 +412,937 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="2">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="B2">
-        <v>322</v>
+        <v>240</v>
       </c>
       <c r="C2">
-        <v>304</v>
+        <v>289</v>
       </c>
       <c r="D2">
-        <v>901.0759710952658</v>
+        <v>879.1356602620498</v>
       </c>
       <c r="E2">
-        <v>626</v>
+        <v>529</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="2">
-        <v>46307.01041666666</v>
+        <v>46308.01041666666</v>
       </c>
       <c r="B3">
-        <v>318</v>
+        <v>218</v>
       </c>
       <c r="C3">
-        <v>307</v>
+        <v>282</v>
       </c>
       <c r="D3">
-        <v>909.4156893812033</v>
+        <v>890.380872335293</v>
       </c>
       <c r="E3">
-        <v>625</v>
+        <v>500</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="2">
-        <v>46307.02083333334</v>
+        <v>46308.02083333334</v>
       </c>
       <c r="B4">
-        <v>318</v>
+        <v>218</v>
       </c>
       <c r="C4">
-        <v>341</v>
+        <v>282</v>
       </c>
       <c r="D4">
-        <v>917.7554076671407</v>
+        <v>901.6260844085361</v>
       </c>
       <c r="E4">
-        <v>659</v>
+        <v>500</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="2">
-        <v>46307.03125</v>
+        <v>46308.03125</v>
       </c>
       <c r="B5">
-        <v>322</v>
+        <v>218</v>
       </c>
       <c r="C5">
-        <v>341</v>
+        <v>281</v>
       </c>
       <c r="D5">
-        <v>926.0951259530782</v>
+        <v>912.8712964817794</v>
       </c>
       <c r="E5">
-        <v>663</v>
+        <v>499</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="2">
-        <v>46307.04166666666</v>
+        <v>46308.04166666666</v>
       </c>
       <c r="B6">
-        <v>400</v>
+        <v>218</v>
       </c>
       <c r="C6">
-        <v>339</v>
+        <v>230</v>
       </c>
       <c r="D6">
-        <v>934.4348442390157</v>
+        <v>924.1165085550226</v>
       </c>
       <c r="E6">
-        <v>739</v>
+        <v>448</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="2">
-        <v>46307.05208333334</v>
+        <v>46308.05208333334</v>
       </c>
       <c r="B7">
-        <v>390</v>
+        <v>217</v>
       </c>
       <c r="C7">
-        <v>309</v>
+        <v>225</v>
       </c>
       <c r="D7">
-        <v>919.2365931542184</v>
+        <v>909.2431794902386</v>
       </c>
       <c r="E7">
-        <v>699</v>
+        <v>442</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="2">
-        <v>46307.0625</v>
+        <v>46308.0625</v>
       </c>
       <c r="B8">
-        <v>390</v>
+        <v>224</v>
       </c>
       <c r="C8">
-        <v>340</v>
+        <v>225</v>
       </c>
       <c r="D8">
-        <v>904.0383420694212</v>
+        <v>894.3698504254547</v>
       </c>
       <c r="E8">
-        <v>730</v>
+        <v>449</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="2">
-        <v>46307.07291666666</v>
+        <v>46308.07291666666</v>
       </c>
       <c r="B9">
-        <v>390</v>
+        <v>224</v>
       </c>
       <c r="C9">
-        <v>323</v>
+        <v>225</v>
       </c>
       <c r="D9">
-        <v>888.840090984624</v>
+        <v>879.4965213606708</v>
       </c>
       <c r="E9">
-        <v>713</v>
+        <v>449</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="2">
-        <v>46307.08333333334</v>
+        <v>46308.08333333334</v>
       </c>
       <c r="B10">
-        <v>405</v>
+        <v>484</v>
       </c>
       <c r="C10">
-        <v>337</v>
+        <v>240</v>
       </c>
       <c r="D10">
-        <v>873.6418398998268</v>
+        <v>864.6231922958868</v>
       </c>
       <c r="E10">
-        <v>742</v>
+        <v>724</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="2">
-        <v>46307.09375</v>
+        <v>46308.09375</v>
       </c>
       <c r="B11">
-        <v>405</v>
+        <v>503</v>
       </c>
       <c r="C11">
-        <v>327</v>
+        <v>241</v>
       </c>
       <c r="D11">
-        <v>846.9697679042205</v>
+        <v>835.3739373022978</v>
       </c>
       <c r="E11">
-        <v>732</v>
+        <v>744</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="2">
-        <v>46307.10416666666</v>
+        <v>46308.10416666666</v>
       </c>
       <c r="B12">
-        <v>406</v>
+        <v>503</v>
       </c>
       <c r="C12">
-        <v>329</v>
+        <v>241</v>
       </c>
       <c r="D12">
-        <v>820.2976959086142</v>
+        <v>806.1246823087088</v>
       </c>
       <c r="E12">
-        <v>735</v>
+        <v>744</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="2">
-        <v>46307.11458333334</v>
+        <v>46308.11458333334</v>
       </c>
       <c r="B13">
-        <v>357</v>
+        <v>502</v>
       </c>
       <c r="C13">
-        <v>327</v>
+        <v>239</v>
       </c>
       <c r="D13">
-        <v>793.6256239130079</v>
+        <v>776.8754273151197</v>
       </c>
       <c r="E13">
-        <v>684</v>
+        <v>741</v>
       </c>
     </row>
     <row r="14" spans="1:5">
       <c r="A14" s="2">
-        <v>46307.125</v>
+        <v>46308.125</v>
       </c>
       <c r="B14">
-        <v>286</v>
+        <v>221</v>
       </c>
       <c r="C14">
-        <v>308</v>
+        <v>166</v>
       </c>
       <c r="D14">
-        <v>766.9535519174016</v>
+        <v>747.6261723215307</v>
       </c>
       <c r="E14">
-        <v>594</v>
+        <v>387</v>
       </c>
     </row>
     <row r="15" spans="1:5">
       <c r="A15" s="2">
-        <v>46307.13541666666</v>
+        <v>46308.13541666666</v>
       </c>
       <c r="B15">
-        <v>282</v>
+        <v>200</v>
       </c>
       <c r="C15">
-        <v>303</v>
+        <v>164</v>
       </c>
       <c r="D15">
-        <v>795.718603405571</v>
+        <v>759.8466846611861</v>
       </c>
       <c r="E15">
-        <v>585</v>
+        <v>364</v>
       </c>
     </row>
     <row r="16" spans="1:5">
       <c r="A16" s="2">
-        <v>46307.14583333334</v>
+        <v>46308.14583333334</v>
       </c>
       <c r="B16">
-        <v>255</v>
+        <v>202</v>
       </c>
       <c r="C16">
-        <v>304</v>
+        <v>164</v>
       </c>
       <c r="D16">
-        <v>824.4836548937404</v>
+        <v>772.0671970008416</v>
       </c>
       <c r="E16">
-        <v>559</v>
+        <v>366</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="2">
-        <v>46307.15625</v>
+        <v>46308.15625</v>
       </c>
       <c r="B17">
-        <v>250</v>
+        <v>201</v>
       </c>
       <c r="C17">
-        <v>304</v>
+        <v>164</v>
       </c>
       <c r="D17">
-        <v>853.2487063819099</v>
+        <v>784.287709340497</v>
       </c>
       <c r="E17">
-        <v>554</v>
+        <v>365</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="2">
-        <v>46307.16666666666</v>
+        <v>46308.16666666666</v>
       </c>
       <c r="B18">
-        <v>114</v>
+        <v>49</v>
       </c>
       <c r="C18">
-        <v>258</v>
+        <v>181</v>
       </c>
       <c r="D18">
-        <v>882.0137578700793</v>
+        <v>796.5082216801525</v>
       </c>
       <c r="E18">
-        <v>372</v>
+        <v>230</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="2">
-        <v>46307.17708333334</v>
+        <v>46308.17708333334</v>
       </c>
       <c r="B19">
-        <v>81</v>
+        <v>45</v>
       </c>
       <c r="C19">
-        <v>261</v>
+        <v>182</v>
       </c>
       <c r="D19">
-        <v>988.0258524778535</v>
+        <v>875.8488983636564</v>
       </c>
       <c r="E19">
-        <v>342</v>
+        <v>227</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="2">
-        <v>46307.1875</v>
+        <v>46308.1875</v>
       </c>
       <c r="B20">
-        <v>80</v>
+        <v>44</v>
       </c>
       <c r="C20">
-        <v>265</v>
+        <v>182</v>
       </c>
       <c r="D20">
-        <v>1094.037947085628</v>
+        <v>955.1895750471604</v>
       </c>
       <c r="E20">
-        <v>345</v>
+        <v>226</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="2">
-        <v>46307.19791666666</v>
+        <v>46308.19791666666</v>
       </c>
       <c r="B21">
-        <v>91</v>
+        <v>47</v>
       </c>
       <c r="C21">
-        <v>266</v>
+        <v>182</v>
       </c>
       <c r="D21">
-        <v>1200.050041693402</v>
+        <v>1034.530251730664</v>
       </c>
       <c r="E21">
-        <v>357</v>
+        <v>229</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="2">
-        <v>46307.20833333334</v>
+        <v>46308.20833333334</v>
       </c>
       <c r="B22">
-        <v>336</v>
+        <v>57</v>
       </c>
       <c r="C22">
-        <v>378</v>
+        <v>193</v>
       </c>
       <c r="D22">
-        <v>1306.062136301176</v>
+        <v>1113.870928414168</v>
       </c>
       <c r="E22">
-        <v>714</v>
+        <v>250</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="2">
-        <v>46307.21875</v>
+        <v>46308.21875</v>
       </c>
       <c r="B23">
-        <v>356</v>
+        <v>71</v>
       </c>
       <c r="C23">
-        <v>390</v>
+        <v>193</v>
       </c>
       <c r="D23">
-        <v>1388.17133178031</v>
+        <v>1198.936617662024</v>
       </c>
       <c r="E23">
-        <v>746</v>
+        <v>264</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="2">
-        <v>46307.22916666666</v>
+        <v>46308.22916666666</v>
       </c>
       <c r="B24">
-        <v>357</v>
+        <v>78</v>
       </c>
       <c r="C24">
-        <v>403</v>
+        <v>193</v>
       </c>
       <c r="D24">
-        <v>1470.280527259444</v>
+        <v>1284.002306909879</v>
       </c>
       <c r="E24">
-        <v>760</v>
+        <v>271</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="2">
-        <v>46307.23958333334</v>
+        <v>46308.23958333334</v>
       </c>
       <c r="B25">
-        <v>386</v>
+        <v>109</v>
       </c>
       <c r="C25">
-        <v>412</v>
+        <v>200</v>
       </c>
       <c r="D25">
-        <v>1552.389722738579</v>
+        <v>1369.067996157735</v>
       </c>
       <c r="E25">
-        <v>798</v>
+        <v>309</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="2">
-        <v>46307.25</v>
+        <v>46308.25</v>
       </c>
       <c r="B26">
-        <v>553</v>
+        <v>799</v>
       </c>
       <c r="C26">
-        <v>451</v>
+        <v>490</v>
       </c>
       <c r="D26">
-        <v>1634.498918217713</v>
+        <v>1454.133685405591</v>
       </c>
       <c r="E26">
-        <v>1004</v>
+        <v>1289</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="2">
-        <v>46307.26041666666</v>
+        <v>46308.26041666666</v>
       </c>
       <c r="B27">
-        <v>654</v>
+        <v>822</v>
       </c>
       <c r="C27">
-        <v>459</v>
+        <v>514</v>
       </c>
       <c r="D27">
-        <v>1642.945968785584</v>
+        <v>1476.331519471946</v>
       </c>
       <c r="E27">
-        <v>1113</v>
+        <v>1336</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="2">
-        <v>46307.27083333334</v>
+        <v>46308.27083333334</v>
       </c>
       <c r="B28">
-        <v>829</v>
+        <v>818</v>
       </c>
       <c r="C28">
-        <v>478</v>
+        <v>513</v>
       </c>
       <c r="D28">
-        <v>1651.393019353454</v>
+        <v>1498.529353538302</v>
       </c>
       <c r="E28">
-        <v>1307</v>
+        <v>1331</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="2">
-        <v>46307.28125</v>
+        <v>46308.28125</v>
       </c>
       <c r="B29">
-        <v>917</v>
+        <v>819</v>
       </c>
       <c r="C29">
-        <v>480</v>
+        <v>516</v>
       </c>
       <c r="D29">
-        <v>1659.840069921325</v>
+        <v>1520.727187604658</v>
       </c>
       <c r="E29">
-        <v>1397</v>
+        <v>1335</v>
       </c>
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="2">
-        <v>46307.29166666666</v>
+        <v>46308.29166666666</v>
       </c>
       <c r="B30">
-        <v>956</v>
+        <v>892</v>
       </c>
       <c r="C30">
-        <v>468</v>
+        <v>514</v>
       </c>
       <c r="D30">
-        <v>1668.287120489196</v>
+        <v>1542.925021671013</v>
       </c>
       <c r="E30">
-        <v>1424</v>
+        <v>1406</v>
       </c>
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="2">
-        <v>46307.30208333334</v>
+        <v>46308.30208333334</v>
       </c>
       <c r="B31">
-        <v>986</v>
+        <v>902</v>
       </c>
       <c r="C31">
-        <v>514</v>
+        <v>526</v>
       </c>
       <c r="D31">
-        <v>1607.011120882393</v>
+        <v>1504.468932161379</v>
       </c>
       <c r="E31">
-        <v>1500</v>
+        <v>1428</v>
       </c>
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="2">
-        <v>46307.3125</v>
+        <v>46308.3125</v>
       </c>
       <c r="B32">
-        <v>1100</v>
+        <v>903</v>
       </c>
       <c r="C32">
-        <v>674</v>
+        <v>527</v>
       </c>
       <c r="D32">
-        <v>1545.735121275591</v>
+        <v>1466.012842651744</v>
       </c>
       <c r="E32">
-        <v>1774</v>
+        <v>1430</v>
       </c>
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="2">
-        <v>46307.32291666666</v>
+        <v>46308.32291666666</v>
       </c>
       <c r="B33">
-        <v>1108</v>
+        <v>903</v>
       </c>
       <c r="C33">
-        <v>678</v>
+        <v>526</v>
       </c>
       <c r="D33">
-        <v>1484.459121668789</v>
+        <v>1427.556753142109</v>
       </c>
       <c r="E33">
-        <v>1786</v>
+        <v>1429</v>
       </c>
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="2">
-        <v>46307.33333333334</v>
+        <v>46308.33333333334</v>
       </c>
       <c r="B34">
-        <v>1273</v>
+        <v>863</v>
       </c>
       <c r="C34">
-        <v>646</v>
+        <v>508</v>
       </c>
       <c r="D34">
-        <v>1423.183122061986</v>
+        <v>1389.100663632474</v>
       </c>
       <c r="E34">
-        <v>1919</v>
+        <v>1371</v>
       </c>
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="2">
-        <v>46307.34375</v>
+        <v>46308.34375</v>
       </c>
       <c r="B35">
-        <v>1218</v>
+        <v>815</v>
       </c>
       <c r="C35">
-        <v>650</v>
+        <v>498</v>
       </c>
       <c r="D35">
-        <v>1204.278933591308</v>
+        <v>1210.591455846917</v>
       </c>
       <c r="E35">
-        <v>1868</v>
+        <v>1313</v>
       </c>
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="2">
-        <v>46307.35416666666</v>
+        <v>46308.35416666666</v>
       </c>
       <c r="B36">
-        <v>1141</v>
+        <v>758</v>
       </c>
       <c r="C36">
-        <v>634</v>
+        <v>506</v>
       </c>
       <c r="D36">
-        <v>985.3747451206298</v>
+        <v>1032.08224806136</v>
       </c>
       <c r="E36">
-        <v>1775</v>
+        <v>1264</v>
       </c>
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="2">
-        <v>46307.36458333334</v>
+        <v>46308.36458333334</v>
       </c>
       <c r="B37">
-        <v>1122</v>
+        <v>743</v>
       </c>
       <c r="C37">
-        <v>638</v>
+        <v>503</v>
       </c>
       <c r="D37">
-        <v>766.4705566499516</v>
+        <v>853.5730402758032</v>
       </c>
       <c r="E37">
-        <v>1760</v>
+        <v>1246</v>
       </c>
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="2">
-        <v>46307.375</v>
+        <v>46308.375</v>
       </c>
       <c r="B38">
-        <v>1050</v>
+        <v>752</v>
       </c>
       <c r="C38">
-        <v>462</v>
+        <v>471</v>
       </c>
       <c r="D38">
-        <v>547.5663681792735</v>
+        <v>675.0638324902462</v>
       </c>
       <c r="E38">
-        <v>1512</v>
+        <v>1223</v>
       </c>
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="2">
-        <v>46307.38541666666</v>
+        <v>46308.38541666666</v>
       </c>
       <c r="B39">
-        <v>1003</v>
+        <v>753</v>
       </c>
       <c r="C39">
-        <v>440</v>
+        <v>468</v>
       </c>
       <c r="D39">
-        <v>498.5155154550628</v>
+        <v>609.2895825146708</v>
       </c>
       <c r="E39">
-        <v>1443</v>
+        <v>1221</v>
       </c>
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="2">
-        <v>46307.39583333334</v>
+        <v>46308.39583333334</v>
       </c>
       <c r="B40">
-        <v>1076</v>
+        <v>881</v>
       </c>
       <c r="C40">
-        <v>438</v>
+        <v>471</v>
       </c>
       <c r="D40">
-        <v>449.4646627308521</v>
+        <v>543.5153325390953</v>
       </c>
       <c r="E40">
-        <v>1514</v>
+        <v>1352</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="2">
+        <v>46308.40625</v>
+      </c>
+      <c r="B41">
+        <v>865</v>
+      </c>
+      <c r="C41">
+        <v>465</v>
+      </c>
+      <c r="D41">
+        <v>477.7410825635198</v>
+      </c>
+      <c r="E41">
+        <v>1330</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="2">
+        <v>46308.41666666666</v>
+      </c>
+      <c r="B42">
+        <v>133</v>
+      </c>
+      <c r="C42">
+        <v>215</v>
+      </c>
+      <c r="D42">
+        <v>411.9668325879443</v>
+      </c>
+      <c r="E42">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="2">
+        <v>46308.42708333334</v>
+      </c>
+      <c r="B43">
+        <v>114</v>
+      </c>
+      <c r="C43">
+        <v>191</v>
+      </c>
+      <c r="D43">
+        <v>410.5233881934828</v>
+      </c>
+      <c r="E43">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="2">
+        <v>46308.4375</v>
+      </c>
+      <c r="B44">
+        <v>115</v>
+      </c>
+      <c r="C44">
+        <v>195</v>
+      </c>
+      <c r="D44">
+        <v>409.0799437990212</v>
+      </c>
+      <c r="E44">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="2">
+        <v>46308.44791666666</v>
+      </c>
+      <c r="B45">
+        <v>111</v>
+      </c>
+      <c r="C45">
+        <v>189</v>
+      </c>
+      <c r="D45">
+        <v>407.6364994045596</v>
+      </c>
+      <c r="E45">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="2">
+        <v>46308.45833333334</v>
+      </c>
+      <c r="B46">
+        <v>54</v>
+      </c>
+      <c r="C46">
+        <v>198</v>
+      </c>
+      <c r="D46">
+        <v>406.193055010098</v>
+      </c>
+      <c r="E46">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" s="2">
+        <v>46308.46875</v>
+      </c>
+      <c r="B47">
+        <v>50</v>
+      </c>
+      <c r="C47">
+        <v>199</v>
+      </c>
+      <c r="D47">
+        <v>399.1416340829452</v>
+      </c>
+      <c r="E47">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" s="2">
+        <v>46308.47916666666</v>
+      </c>
+      <c r="B48">
+        <v>50</v>
+      </c>
+      <c r="C48">
+        <v>201</v>
+      </c>
+      <c r="D48">
+        <v>392.0902131557923</v>
+      </c>
+      <c r="E48">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49" s="2">
+        <v>46308.48958333334</v>
+      </c>
+      <c r="B49">
+        <v>50</v>
+      </c>
+      <c r="C49">
+        <v>199</v>
+      </c>
+      <c r="D49">
+        <v>385.0387922286395</v>
+      </c>
+      <c r="E49">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5">
+      <c r="A50" s="2">
+        <v>46308.5</v>
+      </c>
+      <c r="B50">
+        <v>42</v>
+      </c>
+      <c r="C50">
+        <v>191</v>
+      </c>
+      <c r="D50">
+        <v>377.9873713014866</v>
+      </c>
+      <c r="E50">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5">
+      <c r="A51" s="2">
+        <v>46308.51041666666</v>
+      </c>
+      <c r="B51">
+        <v>44</v>
+      </c>
+      <c r="C51">
+        <v>194</v>
+      </c>
+      <c r="D51">
+        <v>380.4353749704884</v>
+      </c>
+      <c r="E51">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5">
+      <c r="A52" s="2">
+        <v>46308.52083333334</v>
+      </c>
+      <c r="B52">
+        <v>44</v>
+      </c>
+      <c r="C52">
+        <v>168</v>
+      </c>
+      <c r="D52">
+        <v>382.8833786394902</v>
+      </c>
+      <c r="E52">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5">
+      <c r="A53" s="2">
+        <v>46308.53125</v>
+      </c>
+      <c r="B53">
+        <v>51</v>
+      </c>
+      <c r="C53">
+        <v>166</v>
+      </c>
+      <c r="D53">
+        <v>385.3313823084919</v>
+      </c>
+      <c r="E53">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5">
+      <c r="A54" s="2">
+        <v>46308.54166666666</v>
+      </c>
+      <c r="B54">
+        <v>47</v>
+      </c>
+      <c r="C54">
+        <v>204</v>
+      </c>
+      <c r="D54">
+        <v>387.7793859774937</v>
+      </c>
+      <c r="E54">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5">
+      <c r="A55" s="2">
+        <v>46308.55208333334</v>
+      </c>
+      <c r="B55">
+        <v>53</v>
+      </c>
+      <c r="C55">
+        <v>0</v>
+      </c>
+      <c r="D55">
+        <v>380.6206820210882</v>
+      </c>
+      <c r="E55">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5">
+      <c r="A56" s="2">
+        <v>46308.5625</v>
+      </c>
+      <c r="B56">
+        <v>54</v>
+      </c>
+      <c r="C56">
+        <v>0</v>
+      </c>
+      <c r="D56">
+        <v>373.4619780646827</v>
+      </c>
+      <c r="E56">
+        <v>54</v>
       </c>
     </row>
   </sheetData>

--- a/data_fetching/Entsoe/Hydro_Production.xlsx
+++ b/data_fetching/Entsoe/Hydro_Production.xlsx
@@ -390,7 +390,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E56"/>
+  <dimension ref="A1:E60"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:5">
@@ -412,937 +412,1005 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="2">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="B2">
-        <v>240</v>
+        <v>794</v>
       </c>
       <c r="C2">
-        <v>289</v>
+        <v>417</v>
       </c>
       <c r="D2">
-        <v>879.1356602620498</v>
+        <v>832.8119176959298</v>
       </c>
       <c r="E2">
-        <v>529</v>
+        <v>1211</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="2">
-        <v>46308.01041666666</v>
+        <v>46309.01041666666</v>
       </c>
       <c r="B3">
-        <v>218</v>
+        <v>886</v>
       </c>
       <c r="C3">
-        <v>282</v>
+        <v>418</v>
       </c>
       <c r="D3">
-        <v>890.380872335293</v>
+        <v>840.7220559648108</v>
       </c>
       <c r="E3">
-        <v>500</v>
+        <v>1304</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="2">
-        <v>46308.02083333334</v>
+        <v>46309.02083333334</v>
       </c>
       <c r="B4">
-        <v>218</v>
+        <v>883</v>
       </c>
       <c r="C4">
-        <v>282</v>
+        <v>417</v>
       </c>
       <c r="D4">
-        <v>901.6260844085361</v>
+        <v>848.632194233692</v>
       </c>
       <c r="E4">
-        <v>500</v>
+        <v>1300</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="2">
-        <v>46308.03125</v>
+        <v>46309.03125</v>
       </c>
       <c r="B5">
-        <v>218</v>
+        <v>818</v>
       </c>
       <c r="C5">
-        <v>281</v>
+        <v>416</v>
       </c>
       <c r="D5">
-        <v>912.8712964817794</v>
+        <v>856.542332502573</v>
       </c>
       <c r="E5">
-        <v>499</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="2">
-        <v>46308.04166666666</v>
+        <v>46309.04166666666</v>
       </c>
       <c r="B6">
-        <v>218</v>
+        <v>783</v>
       </c>
       <c r="C6">
-        <v>230</v>
+        <v>416</v>
       </c>
       <c r="D6">
-        <v>924.1165085550226</v>
+        <v>864.452470771454</v>
       </c>
       <c r="E6">
-        <v>448</v>
+        <v>1199</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="2">
-        <v>46308.05208333334</v>
+        <v>46309.05208333334</v>
       </c>
       <c r="B7">
-        <v>217</v>
+        <v>729</v>
       </c>
       <c r="C7">
-        <v>225</v>
+        <v>414</v>
       </c>
       <c r="D7">
-        <v>909.2431794902386</v>
+        <v>861.4618368398189</v>
       </c>
       <c r="E7">
-        <v>442</v>
+        <v>1143</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="2">
-        <v>46308.0625</v>
+        <v>46309.0625</v>
       </c>
       <c r="B8">
-        <v>224</v>
+        <v>727</v>
       </c>
       <c r="C8">
-        <v>225</v>
+        <v>415</v>
       </c>
       <c r="D8">
-        <v>894.3698504254547</v>
+        <v>858.4712029081838</v>
       </c>
       <c r="E8">
-        <v>449</v>
+        <v>1142</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="2">
-        <v>46308.07291666666</v>
+        <v>46309.07291666666</v>
       </c>
       <c r="B9">
-        <v>224</v>
+        <v>723</v>
       </c>
       <c r="C9">
-        <v>225</v>
+        <v>415</v>
       </c>
       <c r="D9">
-        <v>879.4965213606708</v>
+        <v>855.4805689765486</v>
       </c>
       <c r="E9">
-        <v>449</v>
+        <v>1138</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="2">
-        <v>46308.08333333334</v>
+        <v>46309.08333333334</v>
       </c>
       <c r="B10">
-        <v>484</v>
+        <v>718</v>
       </c>
       <c r="C10">
-        <v>240</v>
+        <v>415</v>
       </c>
       <c r="D10">
-        <v>864.6231922958868</v>
+        <v>852.4899350449135</v>
       </c>
       <c r="E10">
-        <v>724</v>
+        <v>1133</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="2">
-        <v>46308.09375</v>
+        <v>46309.09375</v>
       </c>
       <c r="B11">
-        <v>503</v>
+        <v>714</v>
       </c>
       <c r="C11">
-        <v>241</v>
+        <v>415</v>
       </c>
       <c r="D11">
-        <v>835.3739373022978</v>
+        <v>812.3729698199198</v>
       </c>
       <c r="E11">
-        <v>744</v>
+        <v>1129</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="2">
-        <v>46308.10416666666</v>
+        <v>46309.10416666666</v>
       </c>
       <c r="B12">
-        <v>503</v>
+        <v>714</v>
       </c>
       <c r="C12">
-        <v>241</v>
+        <v>415</v>
       </c>
       <c r="D12">
-        <v>806.1246823087088</v>
+        <v>772.256004594926</v>
       </c>
       <c r="E12">
-        <v>744</v>
+        <v>1129</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="2">
-        <v>46308.11458333334</v>
+        <v>46309.11458333334</v>
       </c>
       <c r="B13">
-        <v>502</v>
+        <v>714</v>
       </c>
       <c r="C13">
-        <v>239</v>
+        <v>415</v>
       </c>
       <c r="D13">
-        <v>776.8754273151197</v>
+        <v>732.1390393699323</v>
       </c>
       <c r="E13">
-        <v>741</v>
+        <v>1129</v>
       </c>
     </row>
     <row r="14" spans="1:5">
       <c r="A14" s="2">
-        <v>46308.125</v>
+        <v>46309.125</v>
       </c>
       <c r="B14">
-        <v>221</v>
+        <v>701</v>
       </c>
       <c r="C14">
-        <v>166</v>
+        <v>377</v>
       </c>
       <c r="D14">
-        <v>747.6261723215307</v>
+        <v>692.0220741449386</v>
       </c>
       <c r="E14">
-        <v>387</v>
+        <v>1078</v>
       </c>
     </row>
     <row r="15" spans="1:5">
       <c r="A15" s="2">
-        <v>46308.13541666666</v>
+        <v>46309.13541666666</v>
       </c>
       <c r="B15">
-        <v>200</v>
+        <v>699</v>
       </c>
       <c r="C15">
-        <v>164</v>
+        <v>374</v>
       </c>
       <c r="D15">
-        <v>759.8466846611861</v>
+        <v>697.9237097437556</v>
       </c>
       <c r="E15">
-        <v>364</v>
+        <v>1073</v>
       </c>
     </row>
     <row r="16" spans="1:5">
       <c r="A16" s="2">
-        <v>46308.14583333334</v>
+        <v>46309.14583333334</v>
       </c>
       <c r="B16">
-        <v>202</v>
+        <v>701</v>
       </c>
       <c r="C16">
-        <v>164</v>
+        <v>374</v>
       </c>
       <c r="D16">
-        <v>772.0671970008416</v>
+        <v>703.8253453425726</v>
       </c>
       <c r="E16">
-        <v>366</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="2">
-        <v>46308.15625</v>
+        <v>46309.15625</v>
       </c>
       <c r="B17">
-        <v>201</v>
+        <v>701</v>
       </c>
       <c r="C17">
-        <v>164</v>
+        <v>375</v>
       </c>
       <c r="D17">
-        <v>784.287709340497</v>
+        <v>709.7269809413897</v>
       </c>
       <c r="E17">
-        <v>365</v>
+        <v>1076</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="2">
-        <v>46308.16666666666</v>
+        <v>46309.16666666666</v>
       </c>
       <c r="B18">
-        <v>49</v>
+        <v>715</v>
       </c>
       <c r="C18">
-        <v>181</v>
+        <v>375</v>
       </c>
       <c r="D18">
-        <v>796.5082216801525</v>
+        <v>715.6286165402066</v>
       </c>
       <c r="E18">
-        <v>230</v>
+        <v>1090</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="2">
-        <v>46308.17708333334</v>
+        <v>46309.17708333334</v>
       </c>
       <c r="B19">
-        <v>45</v>
+        <v>714</v>
       </c>
       <c r="C19">
-        <v>182</v>
+        <v>375</v>
       </c>
       <c r="D19">
-        <v>875.8488983636564</v>
+        <v>773.1142634451402</v>
       </c>
       <c r="E19">
-        <v>227</v>
+        <v>1089</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="2">
-        <v>46308.1875</v>
+        <v>46309.1875</v>
       </c>
       <c r="B20">
-        <v>44</v>
+        <v>715</v>
       </c>
       <c r="C20">
-        <v>182</v>
+        <v>375</v>
       </c>
       <c r="D20">
-        <v>955.1895750471604</v>
+        <v>830.5999103500737</v>
       </c>
       <c r="E20">
-        <v>226</v>
+        <v>1090</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="2">
-        <v>46308.19791666666</v>
+        <v>46309.19791666666</v>
       </c>
       <c r="B21">
-        <v>47</v>
+        <v>747</v>
       </c>
       <c r="C21">
-        <v>182</v>
+        <v>377</v>
       </c>
       <c r="D21">
-        <v>1034.530251730664</v>
+        <v>888.0855572550073</v>
       </c>
       <c r="E21">
-        <v>229</v>
+        <v>1124</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="2">
-        <v>46308.20833333334</v>
+        <v>46309.20833333334</v>
       </c>
       <c r="B22">
-        <v>57</v>
+        <v>777</v>
       </c>
       <c r="C22">
-        <v>193</v>
+        <v>441</v>
       </c>
       <c r="D22">
-        <v>1113.870928414168</v>
+        <v>945.5712041599409</v>
       </c>
       <c r="E22">
-        <v>250</v>
+        <v>1218</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="2">
-        <v>46308.21875</v>
+        <v>46309.21875</v>
       </c>
       <c r="B23">
-        <v>71</v>
+        <v>787</v>
       </c>
       <c r="C23">
-        <v>193</v>
+        <v>454</v>
       </c>
       <c r="D23">
-        <v>1198.936617662024</v>
+        <v>1034.334634935515</v>
       </c>
       <c r="E23">
-        <v>264</v>
+        <v>1241</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="2">
-        <v>46308.22916666666</v>
+        <v>46309.22916666666</v>
       </c>
       <c r="B24">
-        <v>78</v>
+        <v>839</v>
       </c>
       <c r="C24">
-        <v>193</v>
+        <v>491</v>
       </c>
       <c r="D24">
-        <v>1284.002306909879</v>
+        <v>1123.098065711089</v>
       </c>
       <c r="E24">
-        <v>271</v>
+        <v>1330</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="2">
-        <v>46308.23958333334</v>
+        <v>46309.23958333334</v>
       </c>
       <c r="B25">
-        <v>109</v>
+        <v>875</v>
       </c>
       <c r="C25">
-        <v>200</v>
+        <v>495</v>
       </c>
       <c r="D25">
-        <v>1369.067996157735</v>
+        <v>1211.861496486664</v>
       </c>
       <c r="E25">
-        <v>309</v>
+        <v>1370</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="2">
-        <v>46308.25</v>
+        <v>46309.25</v>
       </c>
       <c r="B26">
-        <v>799</v>
+        <v>935</v>
       </c>
       <c r="C26">
-        <v>490</v>
+        <v>522</v>
       </c>
       <c r="D26">
-        <v>1454.133685405591</v>
+        <v>1300.624927262238</v>
       </c>
       <c r="E26">
-        <v>1289</v>
+        <v>1457</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="2">
-        <v>46308.26041666666</v>
+        <v>46309.26041666666</v>
       </c>
       <c r="B27">
-        <v>822</v>
+        <v>944</v>
       </c>
       <c r="C27">
-        <v>514</v>
+        <v>523</v>
       </c>
       <c r="D27">
-        <v>1476.331519471946</v>
+        <v>1323.461691101144</v>
       </c>
       <c r="E27">
-        <v>1336</v>
+        <v>1467</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="2">
-        <v>46308.27083333334</v>
+        <v>46309.27083333334</v>
       </c>
       <c r="B28">
-        <v>818</v>
+        <v>936</v>
       </c>
       <c r="C28">
-        <v>513</v>
+        <v>525</v>
       </c>
       <c r="D28">
-        <v>1498.529353538302</v>
+        <v>1346.29845494005</v>
       </c>
       <c r="E28">
-        <v>1331</v>
+        <v>1461</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="2">
-        <v>46308.28125</v>
+        <v>46309.28125</v>
       </c>
       <c r="B29">
-        <v>819</v>
+        <v>938</v>
       </c>
       <c r="C29">
-        <v>516</v>
+        <v>526</v>
       </c>
       <c r="D29">
-        <v>1520.727187604658</v>
+        <v>1369.135218778956</v>
       </c>
       <c r="E29">
-        <v>1335</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="2">
-        <v>46308.29166666666</v>
+        <v>46309.29166666666</v>
       </c>
       <c r="B30">
-        <v>892</v>
+        <v>1010</v>
       </c>
       <c r="C30">
-        <v>514</v>
+        <v>536</v>
       </c>
       <c r="D30">
-        <v>1542.925021671013</v>
+        <v>1391.971982617862</v>
       </c>
       <c r="E30">
-        <v>1406</v>
+        <v>1546</v>
       </c>
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="2">
-        <v>46308.30208333334</v>
+        <v>46309.30208333334</v>
       </c>
       <c r="B31">
-        <v>902</v>
+        <v>1024</v>
       </c>
       <c r="C31">
-        <v>526</v>
+        <v>535</v>
       </c>
       <c r="D31">
-        <v>1504.468932161379</v>
+        <v>1355.013763882682</v>
       </c>
       <c r="E31">
-        <v>1428</v>
+        <v>1559</v>
       </c>
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="2">
-        <v>46308.3125</v>
+        <v>46309.3125</v>
       </c>
       <c r="B32">
-        <v>903</v>
+        <v>1016</v>
       </c>
       <c r="C32">
-        <v>527</v>
+        <v>539</v>
       </c>
       <c r="D32">
-        <v>1466.012842651744</v>
+        <v>1318.055545147501</v>
       </c>
       <c r="E32">
-        <v>1430</v>
+        <v>1555</v>
       </c>
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="2">
-        <v>46308.32291666666</v>
+        <v>46309.32291666666</v>
       </c>
       <c r="B33">
-        <v>903</v>
+        <v>1019</v>
       </c>
       <c r="C33">
-        <v>526</v>
+        <v>505</v>
       </c>
       <c r="D33">
-        <v>1427.556753142109</v>
+        <v>1281.09732641232</v>
       </c>
       <c r="E33">
-        <v>1429</v>
+        <v>1524</v>
       </c>
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="2">
-        <v>46308.33333333334</v>
+        <v>46309.33333333334</v>
       </c>
       <c r="B34">
-        <v>863</v>
+        <v>1020</v>
       </c>
       <c r="C34">
-        <v>508</v>
+        <v>494</v>
       </c>
       <c r="D34">
-        <v>1389.100663632474</v>
+        <v>1244.13910767714</v>
       </c>
       <c r="E34">
-        <v>1371</v>
+        <v>1514</v>
       </c>
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="2">
-        <v>46308.34375</v>
+        <v>46309.34375</v>
       </c>
       <c r="B35">
-        <v>815</v>
+        <v>911</v>
       </c>
       <c r="C35">
-        <v>498</v>
+        <v>486</v>
       </c>
       <c r="D35">
-        <v>1210.591455846917</v>
+        <v>1121.593900715319</v>
       </c>
       <c r="E35">
-        <v>1313</v>
+        <v>1397</v>
       </c>
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="2">
-        <v>46308.35416666666</v>
+        <v>46309.35416666666</v>
       </c>
       <c r="B36">
-        <v>758</v>
+        <v>832</v>
       </c>
       <c r="C36">
-        <v>506</v>
+        <v>480</v>
       </c>
       <c r="D36">
-        <v>1032.08224806136</v>
+        <v>999.0486937534989</v>
       </c>
       <c r="E36">
-        <v>1264</v>
+        <v>1312</v>
       </c>
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="2">
-        <v>46308.36458333334</v>
+        <v>46309.36458333334</v>
       </c>
       <c r="B37">
-        <v>743</v>
+        <v>825</v>
       </c>
       <c r="C37">
-        <v>503</v>
+        <v>483</v>
       </c>
       <c r="D37">
-        <v>853.5730402758032</v>
+        <v>876.5034867916786</v>
       </c>
       <c r="E37">
-        <v>1246</v>
+        <v>1308</v>
       </c>
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="2">
-        <v>46308.375</v>
+        <v>46309.375</v>
       </c>
       <c r="B38">
-        <v>752</v>
+        <v>871</v>
       </c>
       <c r="C38">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="D38">
-        <v>675.0638324902462</v>
+        <v>753.9582798298582</v>
       </c>
       <c r="E38">
-        <v>1223</v>
+        <v>1341</v>
       </c>
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="2">
-        <v>46308.38541666666</v>
+        <v>46309.38541666666</v>
       </c>
       <c r="B39">
-        <v>753</v>
+        <v>793</v>
       </c>
       <c r="C39">
         <v>468</v>
       </c>
       <c r="D39">
-        <v>609.2895825146708</v>
+        <v>659.5763503957269</v>
       </c>
       <c r="E39">
-        <v>1221</v>
+        <v>1261</v>
       </c>
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="2">
-        <v>46308.39583333334</v>
+        <v>46309.39583333334</v>
       </c>
       <c r="B40">
-        <v>881</v>
+        <v>826</v>
       </c>
       <c r="C40">
-        <v>471</v>
+        <v>486</v>
       </c>
       <c r="D40">
-        <v>543.5153325390953</v>
+        <v>565.1944209615956</v>
       </c>
       <c r="E40">
-        <v>1352</v>
+        <v>1312</v>
       </c>
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="2">
-        <v>46308.40625</v>
+        <v>46309.40625</v>
       </c>
       <c r="B41">
-        <v>865</v>
+        <v>858</v>
       </c>
       <c r="C41">
-        <v>465</v>
+        <v>484</v>
       </c>
       <c r="D41">
-        <v>477.7410825635198</v>
+        <v>470.8124915274643</v>
       </c>
       <c r="E41">
-        <v>1330</v>
+        <v>1342</v>
       </c>
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="2">
-        <v>46308.41666666666</v>
+        <v>46309.41666666666</v>
       </c>
       <c r="B42">
-        <v>133</v>
+        <v>782</v>
       </c>
       <c r="C42">
-        <v>215</v>
+        <v>440</v>
       </c>
       <c r="D42">
-        <v>411.9668325879443</v>
+        <v>376.430562093333</v>
       </c>
       <c r="E42">
-        <v>348</v>
+        <v>1222</v>
       </c>
     </row>
     <row r="43" spans="1:5">
       <c r="A43" s="2">
-        <v>46308.42708333334</v>
+        <v>46309.42708333334</v>
       </c>
       <c r="B43">
-        <v>114</v>
+        <v>785</v>
       </c>
       <c r="C43">
-        <v>191</v>
+        <v>437</v>
       </c>
       <c r="D43">
-        <v>410.5233881934828</v>
+        <v>373.0860069863328</v>
       </c>
       <c r="E43">
-        <v>305</v>
+        <v>1222</v>
       </c>
     </row>
     <row r="44" spans="1:5">
       <c r="A44" s="2">
-        <v>46308.4375</v>
+        <v>46309.4375</v>
       </c>
       <c r="B44">
-        <v>115</v>
+        <v>785</v>
       </c>
       <c r="C44">
-        <v>195</v>
+        <v>426</v>
       </c>
       <c r="D44">
-        <v>409.0799437990212</v>
+        <v>369.7414518793325</v>
       </c>
       <c r="E44">
-        <v>310</v>
+        <v>1211</v>
       </c>
     </row>
     <row r="45" spans="1:5">
       <c r="A45" s="2">
-        <v>46308.44791666666</v>
+        <v>46309.44791666666</v>
       </c>
       <c r="B45">
-        <v>111</v>
+        <v>781</v>
       </c>
       <c r="C45">
-        <v>189</v>
+        <v>417</v>
       </c>
       <c r="D45">
-        <v>407.6364994045596</v>
+        <v>366.3968967723323</v>
       </c>
       <c r="E45">
-        <v>300</v>
+        <v>1198</v>
       </c>
     </row>
     <row r="46" spans="1:5">
       <c r="A46" s="2">
-        <v>46308.45833333334</v>
+        <v>46309.45833333334</v>
       </c>
       <c r="B46">
-        <v>54</v>
+        <v>719</v>
       </c>
       <c r="C46">
-        <v>198</v>
+        <v>427</v>
       </c>
       <c r="D46">
-        <v>406.193055010098</v>
+        <v>363.0523416653321</v>
       </c>
       <c r="E46">
-        <v>252</v>
+        <v>1146</v>
       </c>
     </row>
     <row r="47" spans="1:5">
       <c r="A47" s="2">
-        <v>46308.46875</v>
+        <v>46309.46875</v>
       </c>
       <c r="B47">
-        <v>50</v>
+        <v>716</v>
       </c>
       <c r="C47">
-        <v>199</v>
+        <v>429</v>
       </c>
       <c r="D47">
-        <v>399.1416340829452</v>
+        <v>355.7881095413863</v>
       </c>
       <c r="E47">
-        <v>249</v>
+        <v>1145</v>
       </c>
     </row>
     <row r="48" spans="1:5">
       <c r="A48" s="2">
-        <v>46308.47916666666</v>
+        <v>46309.47916666666</v>
       </c>
       <c r="B48">
-        <v>50</v>
+        <v>714</v>
       </c>
       <c r="C48">
-        <v>201</v>
+        <v>437</v>
       </c>
       <c r="D48">
-        <v>392.0902131557923</v>
+        <v>348.5238774174406</v>
       </c>
       <c r="E48">
-        <v>251</v>
+        <v>1151</v>
       </c>
     </row>
     <row r="49" spans="1:5">
       <c r="A49" s="2">
-        <v>46308.48958333334</v>
+        <v>46309.48958333334</v>
       </c>
       <c r="B49">
-        <v>50</v>
+        <v>683</v>
       </c>
       <c r="C49">
-        <v>199</v>
+        <v>459</v>
       </c>
       <c r="D49">
-        <v>385.0387922286395</v>
+        <v>341.2596452934949</v>
       </c>
       <c r="E49">
-        <v>249</v>
+        <v>1142</v>
       </c>
     </row>
     <row r="50" spans="1:5">
       <c r="A50" s="2">
-        <v>46308.5</v>
+        <v>46309.5</v>
       </c>
       <c r="B50">
-        <v>42</v>
+        <v>447</v>
       </c>
       <c r="C50">
-        <v>191</v>
+        <v>455</v>
       </c>
       <c r="D50">
-        <v>377.9873713014866</v>
+        <v>333.9954131695492</v>
       </c>
       <c r="E50">
-        <v>233</v>
+        <v>902</v>
       </c>
     </row>
     <row r="51" spans="1:5">
       <c r="A51" s="2">
-        <v>46308.51041666666</v>
+        <v>46309.51041666666</v>
       </c>
       <c r="B51">
-        <v>44</v>
+        <v>432</v>
       </c>
       <c r="C51">
-        <v>194</v>
+        <v>453</v>
       </c>
       <c r="D51">
-        <v>380.4353749704884</v>
+        <v>337.1718557182582</v>
       </c>
       <c r="E51">
-        <v>238</v>
+        <v>885</v>
       </c>
     </row>
     <row r="52" spans="1:5">
       <c r="A52" s="2">
-        <v>46308.52083333334</v>
+        <v>46309.52083333334</v>
       </c>
       <c r="B52">
-        <v>44</v>
+        <v>415</v>
       </c>
       <c r="C52">
-        <v>168</v>
+        <v>448</v>
       </c>
       <c r="D52">
-        <v>382.8833786394902</v>
+        <v>340.3482982669672</v>
       </c>
       <c r="E52">
-        <v>212</v>
+        <v>863</v>
       </c>
     </row>
     <row r="53" spans="1:5">
       <c r="A53" s="2">
-        <v>46308.53125</v>
+        <v>46309.53125</v>
       </c>
       <c r="B53">
-        <v>51</v>
+        <v>224</v>
       </c>
       <c r="C53">
-        <v>166</v>
+        <v>379</v>
       </c>
       <c r="D53">
-        <v>385.3313823084919</v>
+        <v>343.5247408156761</v>
       </c>
       <c r="E53">
-        <v>217</v>
+        <v>603</v>
       </c>
     </row>
     <row r="54" spans="1:5">
       <c r="A54" s="2">
-        <v>46308.54166666666</v>
+        <v>46309.54166666666</v>
       </c>
       <c r="B54">
-        <v>47</v>
+        <v>238</v>
       </c>
       <c r="C54">
-        <v>204</v>
+        <v>305</v>
       </c>
       <c r="D54">
-        <v>387.7793859774937</v>
+        <v>346.701183364385</v>
       </c>
       <c r="E54">
-        <v>251</v>
+        <v>543</v>
       </c>
     </row>
     <row r="55" spans="1:5">
       <c r="A55" s="2">
-        <v>46308.55208333334</v>
+        <v>46309.55208333334</v>
       </c>
       <c r="B55">
-        <v>53</v>
+        <v>174</v>
       </c>
       <c r="C55">
-        <v>0</v>
+        <v>269</v>
       </c>
       <c r="D55">
-        <v>380.6206820210882</v>
+        <v>340.7199155011359</v>
       </c>
       <c r="E55">
-        <v>53</v>
+        <v>443</v>
       </c>
     </row>
     <row r="56" spans="1:5">
       <c r="A56" s="2">
-        <v>46308.5625</v>
+        <v>46309.5625</v>
       </c>
       <c r="B56">
-        <v>54</v>
+        <v>164</v>
       </c>
       <c r="C56">
+        <v>266</v>
+      </c>
+      <c r="D56">
+        <v>334.7386476378866</v>
+      </c>
+      <c r="E56">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5">
+      <c r="A57" s="2">
+        <v>46309.57291666666</v>
+      </c>
+      <c r="B57">
+        <v>291</v>
+      </c>
+      <c r="C57">
+        <v>278</v>
+      </c>
+      <c r="D57">
+        <v>328.7573797746375</v>
+      </c>
+      <c r="E57">
+        <v>569</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5">
+      <c r="A58" s="2">
+        <v>46309.58333333334</v>
+      </c>
+      <c r="B58">
+        <v>151</v>
+      </c>
+      <c r="C58">
+        <v>329</v>
+      </c>
+      <c r="D58">
+        <v>322.7761119113883</v>
+      </c>
+      <c r="E58">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5">
+      <c r="A59" s="2">
+        <v>46309.59375</v>
+      </c>
+      <c r="B59">
+        <v>160</v>
+      </c>
+      <c r="C59">
+        <v>330</v>
+      </c>
+      <c r="D59">
+        <v>334.1192855811037</v>
+      </c>
+      <c r="E59">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5">
+      <c r="A60" s="2">
+        <v>46309.60416666666</v>
+      </c>
+      <c r="B60">
+        <v>137</v>
+      </c>
+      <c r="C60">
         <v>0</v>
       </c>
-      <c r="D56">
-        <v>373.4619780646827</v>
-      </c>
-      <c r="E56">
-        <v>54</v>
+      <c r="D60">
+        <v>345.4624592508191</v>
+      </c>
+      <c r="E60">
+        <v>137</v>
       </c>
     </row>
   </sheetData>

--- a/data_fetching/Entsoe/Hydro_Production.xlsx
+++ b/data_fetching/Entsoe/Hydro_Production.xlsx
@@ -390,7 +390,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E60"/>
+  <dimension ref="A1:E52"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:5">
@@ -412,1005 +412,869 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="2">
-        <v>46309</v>
+        <v>46311</v>
       </c>
       <c r="B2">
-        <v>794</v>
+        <v>737</v>
       </c>
       <c r="C2">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="D2">
-        <v>832.8119176959298</v>
+        <v>1167.045709619204</v>
       </c>
       <c r="E2">
-        <v>1211</v>
+        <v>1157</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="2">
-        <v>46309.01041666666</v>
+        <v>46311.01041666666</v>
       </c>
       <c r="B3">
-        <v>886</v>
+        <v>733</v>
       </c>
       <c r="C3">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="D3">
-        <v>840.7220559648108</v>
+        <v>1141.646428579514</v>
       </c>
       <c r="E3">
-        <v>1304</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="2">
-        <v>46309.02083333334</v>
+        <v>46311.02083333334</v>
       </c>
       <c r="B4">
-        <v>883</v>
+        <v>734</v>
       </c>
       <c r="C4">
         <v>417</v>
       </c>
       <c r="D4">
-        <v>848.632194233692</v>
+        <v>1116.247147539824</v>
       </c>
       <c r="E4">
-        <v>1300</v>
+        <v>1151</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="2">
-        <v>46309.03125</v>
+        <v>46311.03125</v>
       </c>
       <c r="B5">
-        <v>818</v>
+        <v>730</v>
       </c>
       <c r="C5">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="D5">
-        <v>856.542332502573</v>
+        <v>1090.847866500133</v>
       </c>
       <c r="E5">
-        <v>1234</v>
+        <v>1147</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="2">
-        <v>46309.04166666666</v>
+        <v>46311.04166666666</v>
       </c>
       <c r="B6">
-        <v>783</v>
+        <v>452</v>
       </c>
       <c r="C6">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="D6">
-        <v>864.452470771454</v>
+        <v>1065.448585460443</v>
       </c>
       <c r="E6">
-        <v>1199</v>
+        <v>870</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="2">
-        <v>46309.05208333334</v>
+        <v>46311.05208333334</v>
       </c>
       <c r="B7">
-        <v>729</v>
+        <v>447</v>
       </c>
       <c r="C7">
-        <v>414</v>
+        <v>418</v>
       </c>
       <c r="D7">
-        <v>861.4618368398189</v>
+        <v>1061.507710465047</v>
       </c>
       <c r="E7">
-        <v>1143</v>
+        <v>865</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="2">
-        <v>46309.0625</v>
+        <v>46311.0625</v>
       </c>
       <c r="B8">
-        <v>727</v>
+        <v>448</v>
       </c>
       <c r="C8">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="D8">
-        <v>858.4712029081838</v>
+        <v>1057.566835469651</v>
       </c>
       <c r="E8">
-        <v>1142</v>
+        <v>865</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="2">
-        <v>46309.07291666666</v>
+        <v>46311.07291666666</v>
       </c>
       <c r="B9">
-        <v>723</v>
+        <v>447</v>
       </c>
       <c r="C9">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="D9">
-        <v>855.4805689765486</v>
+        <v>1053.625960474256</v>
       </c>
       <c r="E9">
-        <v>1138</v>
+        <v>864</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="2">
-        <v>46309.08333333334</v>
+        <v>46311.08333333334</v>
       </c>
       <c r="B10">
-        <v>718</v>
+        <v>444</v>
       </c>
       <c r="C10">
-        <v>415</v>
+        <v>412</v>
       </c>
       <c r="D10">
-        <v>852.4899350449135</v>
+        <v>1049.68508547886</v>
       </c>
       <c r="E10">
-        <v>1133</v>
+        <v>856</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="2">
-        <v>46309.09375</v>
+        <v>46311.09375</v>
       </c>
       <c r="B11">
-        <v>714</v>
+        <v>443</v>
       </c>
       <c r="C11">
-        <v>415</v>
+        <v>412</v>
       </c>
       <c r="D11">
-        <v>812.3729698199198</v>
+        <v>996.6882896593106</v>
       </c>
       <c r="E11">
-        <v>1129</v>
+        <v>855</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="2">
-        <v>46309.10416666666</v>
+        <v>46311.10416666666</v>
       </c>
       <c r="B12">
-        <v>714</v>
+        <v>443</v>
       </c>
       <c r="C12">
-        <v>415</v>
+        <v>412</v>
       </c>
       <c r="D12">
-        <v>772.256004594926</v>
+        <v>943.6914938397615</v>
       </c>
       <c r="E12">
-        <v>1129</v>
+        <v>855</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="2">
-        <v>46309.11458333334</v>
+        <v>46311.11458333334</v>
       </c>
       <c r="B13">
-        <v>714</v>
+        <v>444</v>
       </c>
       <c r="C13">
-        <v>415</v>
+        <v>412</v>
       </c>
       <c r="D13">
-        <v>732.1390393699323</v>
+        <v>890.6946980202123</v>
       </c>
       <c r="E13">
-        <v>1129</v>
+        <v>856</v>
       </c>
     </row>
     <row r="14" spans="1:5">
       <c r="A14" s="2">
-        <v>46309.125</v>
+        <v>46311.125</v>
       </c>
       <c r="B14">
-        <v>701</v>
+        <v>414</v>
       </c>
       <c r="C14">
-        <v>377</v>
+        <v>403</v>
       </c>
       <c r="D14">
-        <v>692.0220741449386</v>
+        <v>837.6979022006632</v>
       </c>
       <c r="E14">
-        <v>1078</v>
+        <v>817</v>
       </c>
     </row>
     <row r="15" spans="1:5">
       <c r="A15" s="2">
-        <v>46309.13541666666</v>
+        <v>46311.13541666666</v>
       </c>
       <c r="B15">
-        <v>699</v>
+        <v>413</v>
       </c>
       <c r="C15">
-        <v>374</v>
+        <v>403</v>
       </c>
       <c r="D15">
-        <v>697.9237097437556</v>
+        <v>843.1991814571652</v>
       </c>
       <c r="E15">
-        <v>1073</v>
+        <v>816</v>
       </c>
     </row>
     <row r="16" spans="1:5">
       <c r="A16" s="2">
-        <v>46309.14583333334</v>
+        <v>46311.14583333334</v>
       </c>
       <c r="B16">
-        <v>701</v>
+        <v>412</v>
       </c>
       <c r="C16">
-        <v>374</v>
+        <v>403</v>
       </c>
       <c r="D16">
-        <v>703.8253453425726</v>
+        <v>848.7004607136672</v>
       </c>
       <c r="E16">
-        <v>1075</v>
+        <v>815</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="2">
-        <v>46309.15625</v>
+        <v>46311.15625</v>
       </c>
       <c r="B17">
-        <v>701</v>
+        <v>419</v>
       </c>
       <c r="C17">
-        <v>375</v>
+        <v>402</v>
       </c>
       <c r="D17">
-        <v>709.7269809413897</v>
+        <v>854.2017399701692</v>
       </c>
       <c r="E17">
-        <v>1076</v>
+        <v>821</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="2">
-        <v>46309.16666666666</v>
+        <v>46311.16666666666</v>
       </c>
       <c r="B18">
-        <v>715</v>
+        <v>652</v>
       </c>
       <c r="C18">
-        <v>375</v>
+        <v>403</v>
       </c>
       <c r="D18">
-        <v>715.6286165402066</v>
+        <v>859.7030192266712</v>
       </c>
       <c r="E18">
-        <v>1090</v>
+        <v>1055</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="2">
-        <v>46309.17708333334</v>
+        <v>46311.17708333334</v>
       </c>
       <c r="B19">
-        <v>714</v>
+        <v>666</v>
       </c>
       <c r="C19">
-        <v>375</v>
+        <v>403</v>
       </c>
       <c r="D19">
-        <v>773.1142634451402</v>
+        <v>934.032933157264</v>
       </c>
       <c r="E19">
-        <v>1089</v>
+        <v>1069</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="2">
-        <v>46309.1875</v>
+        <v>46311.1875</v>
       </c>
       <c r="B20">
-        <v>715</v>
+        <v>677</v>
       </c>
       <c r="C20">
-        <v>375</v>
+        <v>403</v>
       </c>
       <c r="D20">
-        <v>830.5999103500737</v>
+        <v>1008.362847087857</v>
       </c>
       <c r="E20">
-        <v>1090</v>
+        <v>1080</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="2">
-        <v>46309.19791666666</v>
+        <v>46311.19791666666</v>
       </c>
       <c r="B21">
-        <v>747</v>
+        <v>685</v>
       </c>
       <c r="C21">
-        <v>377</v>
+        <v>402</v>
       </c>
       <c r="D21">
-        <v>888.0855572550073</v>
+        <v>1082.69276101845</v>
       </c>
       <c r="E21">
-        <v>1124</v>
+        <v>1087</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="2">
-        <v>46309.20833333334</v>
+        <v>46311.20833333334</v>
       </c>
       <c r="B22">
-        <v>777</v>
+        <v>822</v>
       </c>
       <c r="C22">
-        <v>441</v>
+        <v>417</v>
       </c>
       <c r="D22">
-        <v>945.5712041599409</v>
+        <v>1157.022674949042</v>
       </c>
       <c r="E22">
-        <v>1218</v>
+        <v>1239</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="2">
-        <v>46309.21875</v>
+        <v>46311.21875</v>
       </c>
       <c r="B23">
-        <v>787</v>
+        <v>828</v>
       </c>
       <c r="C23">
-        <v>454</v>
+        <v>420</v>
       </c>
       <c r="D23">
-        <v>1034.334634935515</v>
+        <v>1288.939478985624</v>
       </c>
       <c r="E23">
-        <v>1241</v>
+        <v>1248</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="2">
-        <v>46309.22916666666</v>
+        <v>46311.22916666666</v>
       </c>
       <c r="B24">
-        <v>839</v>
+        <v>828</v>
       </c>
       <c r="C24">
-        <v>491</v>
+        <v>421</v>
       </c>
       <c r="D24">
-        <v>1123.098065711089</v>
+        <v>1420.856283022205</v>
       </c>
       <c r="E24">
-        <v>1330</v>
+        <v>1249</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="2">
-        <v>46309.23958333334</v>
+        <v>46311.23958333334</v>
       </c>
       <c r="B25">
-        <v>875</v>
+        <v>836</v>
       </c>
       <c r="C25">
-        <v>495</v>
+        <v>421</v>
       </c>
       <c r="D25">
-        <v>1211.861496486664</v>
+        <v>1552.773087058786</v>
       </c>
       <c r="E25">
-        <v>1370</v>
+        <v>1257</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="2">
-        <v>46309.25</v>
+        <v>46311.25</v>
       </c>
       <c r="B26">
-        <v>935</v>
+        <v>1008</v>
       </c>
       <c r="C26">
-        <v>522</v>
+        <v>416</v>
       </c>
       <c r="D26">
-        <v>1300.624927262238</v>
+        <v>1684.689891095368</v>
       </c>
       <c r="E26">
-        <v>1457</v>
+        <v>1424</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="2">
-        <v>46309.26041666666</v>
+        <v>46311.26041666666</v>
       </c>
       <c r="B27">
-        <v>944</v>
+        <v>1026</v>
       </c>
       <c r="C27">
-        <v>523</v>
+        <v>411</v>
       </c>
       <c r="D27">
-        <v>1323.461691101144</v>
+        <v>1720.860137801665</v>
       </c>
       <c r="E27">
-        <v>1467</v>
+        <v>1437</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="2">
-        <v>46309.27083333334</v>
+        <v>46311.27083333334</v>
       </c>
       <c r="B28">
-        <v>936</v>
+        <v>1019</v>
       </c>
       <c r="C28">
-        <v>525</v>
+        <v>414</v>
       </c>
       <c r="D28">
-        <v>1346.29845494005</v>
+        <v>1757.030384507962</v>
       </c>
       <c r="E28">
-        <v>1461</v>
+        <v>1433</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="2">
-        <v>46309.28125</v>
+        <v>46311.28125</v>
       </c>
       <c r="B29">
-        <v>938</v>
+        <v>1015</v>
       </c>
       <c r="C29">
-        <v>526</v>
+        <v>415</v>
       </c>
       <c r="D29">
-        <v>1369.135218778956</v>
+        <v>1793.20063121426</v>
       </c>
       <c r="E29">
-        <v>1464</v>
+        <v>1430</v>
       </c>
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="2">
-        <v>46309.29166666666</v>
+        <v>46311.29166666666</v>
       </c>
       <c r="B30">
-        <v>1010</v>
+        <v>1040</v>
       </c>
       <c r="C30">
-        <v>536</v>
+        <v>449</v>
       </c>
       <c r="D30">
-        <v>1391.971982617862</v>
+        <v>1829.370877920557</v>
       </c>
       <c r="E30">
-        <v>1546</v>
+        <v>1489</v>
       </c>
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="2">
-        <v>46309.30208333334</v>
+        <v>46311.30208333334</v>
       </c>
       <c r="B31">
-        <v>1024</v>
+        <v>1027</v>
       </c>
       <c r="C31">
-        <v>535</v>
+        <v>448</v>
       </c>
       <c r="D31">
-        <v>1355.013763882682</v>
+        <v>1788.154944442698</v>
       </c>
       <c r="E31">
-        <v>1559</v>
+        <v>1475</v>
       </c>
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="2">
-        <v>46309.3125</v>
+        <v>46311.3125</v>
       </c>
       <c r="B32">
-        <v>1016</v>
+        <v>1024</v>
       </c>
       <c r="C32">
-        <v>539</v>
+        <v>458</v>
       </c>
       <c r="D32">
-        <v>1318.055545147501</v>
+        <v>1746.939010964839</v>
       </c>
       <c r="E32">
-        <v>1555</v>
+        <v>1482</v>
       </c>
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="2">
-        <v>46309.32291666666</v>
+        <v>46311.32291666666</v>
       </c>
       <c r="B33">
-        <v>1019</v>
+        <v>1022</v>
       </c>
       <c r="C33">
-        <v>505</v>
+        <v>459</v>
       </c>
       <c r="D33">
-        <v>1281.09732641232</v>
+        <v>1705.72307748698</v>
       </c>
       <c r="E33">
-        <v>1524</v>
+        <v>1481</v>
       </c>
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="2">
-        <v>46309.33333333334</v>
+        <v>46311.33333333334</v>
       </c>
       <c r="B34">
-        <v>1020</v>
+        <v>997</v>
       </c>
       <c r="C34">
-        <v>494</v>
+        <v>446</v>
       </c>
       <c r="D34">
-        <v>1244.13910767714</v>
+        <v>1664.507144009121</v>
       </c>
       <c r="E34">
-        <v>1514</v>
+        <v>1443</v>
       </c>
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="2">
-        <v>46309.34375</v>
+        <v>46311.34375</v>
       </c>
       <c r="B35">
-        <v>911</v>
+        <v>987</v>
       </c>
       <c r="C35">
-        <v>486</v>
+        <v>443</v>
       </c>
       <c r="D35">
-        <v>1121.593900715319</v>
+        <v>1570.757600404775</v>
       </c>
       <c r="E35">
-        <v>1397</v>
+        <v>1430</v>
       </c>
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="2">
-        <v>46309.35416666666</v>
+        <v>46311.35416666666</v>
       </c>
       <c r="B36">
-        <v>832</v>
+        <v>995</v>
       </c>
       <c r="C36">
-        <v>480</v>
+        <v>445</v>
       </c>
       <c r="D36">
-        <v>999.0486937534989</v>
+        <v>1477.008056800429</v>
       </c>
       <c r="E36">
-        <v>1312</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="2">
-        <v>46309.36458333334</v>
+        <v>46311.36458333334</v>
       </c>
       <c r="B37">
-        <v>825</v>
+        <v>983</v>
       </c>
       <c r="C37">
-        <v>483</v>
+        <v>457</v>
       </c>
       <c r="D37">
-        <v>876.5034867916786</v>
+        <v>1383.258513196084</v>
       </c>
       <c r="E37">
-        <v>1308</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="2">
-        <v>46309.375</v>
+        <v>46311.375</v>
       </c>
       <c r="B38">
-        <v>871</v>
+        <v>898</v>
       </c>
       <c r="C38">
-        <v>470</v>
+        <v>440</v>
       </c>
       <c r="D38">
-        <v>753.9582798298582</v>
+        <v>1289.508969591738</v>
       </c>
       <c r="E38">
-        <v>1341</v>
+        <v>1338</v>
       </c>
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="2">
-        <v>46309.38541666666</v>
+        <v>46311.38541666666</v>
       </c>
       <c r="B39">
-        <v>793</v>
+        <v>896</v>
       </c>
       <c r="C39">
-        <v>468</v>
+        <v>440</v>
       </c>
       <c r="D39">
-        <v>659.5763503957269</v>
+        <v>1156.920166639705</v>
       </c>
       <c r="E39">
-        <v>1261</v>
+        <v>1336</v>
       </c>
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="2">
-        <v>46309.39583333334</v>
+        <v>46311.39583333334</v>
       </c>
       <c r="B40">
-        <v>826</v>
+        <v>895</v>
       </c>
       <c r="C40">
-        <v>486</v>
+        <v>438</v>
       </c>
       <c r="D40">
-        <v>565.1944209615956</v>
+        <v>1024.331363687671</v>
       </c>
       <c r="E40">
-        <v>1312</v>
+        <v>1333</v>
       </c>
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="2">
-        <v>46309.40625</v>
+        <v>46311.40625</v>
       </c>
       <c r="B41">
-        <v>858</v>
+        <v>736</v>
       </c>
       <c r="C41">
-        <v>484</v>
+        <v>438</v>
       </c>
       <c r="D41">
-        <v>470.8124915274643</v>
+        <v>891.7425607356377</v>
       </c>
       <c r="E41">
-        <v>1342</v>
+        <v>1174</v>
       </c>
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="2">
-        <v>46309.41666666666</v>
+        <v>46311.41666666666</v>
       </c>
       <c r="B42">
-        <v>782</v>
+        <v>70</v>
       </c>
       <c r="C42">
-        <v>440</v>
+        <v>184</v>
       </c>
       <c r="D42">
-        <v>376.430562093333</v>
+        <v>759.1537577836041</v>
       </c>
       <c r="E42">
-        <v>1222</v>
+        <v>254</v>
       </c>
     </row>
     <row r="43" spans="1:5">
       <c r="A43" s="2">
-        <v>46309.42708333334</v>
+        <v>46311.42708333334</v>
       </c>
       <c r="B43">
-        <v>785</v>
+        <v>51</v>
       </c>
       <c r="C43">
-        <v>437</v>
+        <v>208</v>
       </c>
       <c r="D43">
-        <v>373.0860069863328</v>
+        <v>759.4385030867396</v>
       </c>
       <c r="E43">
-        <v>1222</v>
+        <v>259</v>
       </c>
     </row>
     <row r="44" spans="1:5">
       <c r="A44" s="2">
-        <v>46309.4375</v>
+        <v>46311.4375</v>
       </c>
       <c r="B44">
-        <v>785</v>
+        <v>50</v>
       </c>
       <c r="C44">
-        <v>426</v>
+        <v>207</v>
       </c>
       <c r="D44">
-        <v>369.7414518793325</v>
+        <v>759.7232483898752</v>
       </c>
       <c r="E44">
-        <v>1211</v>
+        <v>257</v>
       </c>
     </row>
     <row r="45" spans="1:5">
       <c r="A45" s="2">
-        <v>46309.44791666666</v>
+        <v>46311.44791666666</v>
       </c>
       <c r="B45">
-        <v>781</v>
+        <v>48</v>
       </c>
       <c r="C45">
-        <v>417</v>
+        <v>207</v>
       </c>
       <c r="D45">
-        <v>366.3968967723323</v>
+        <v>760.0079936930108</v>
       </c>
       <c r="E45">
-        <v>1198</v>
+        <v>255</v>
       </c>
     </row>
     <row r="46" spans="1:5">
       <c r="A46" s="2">
-        <v>46309.45833333334</v>
+        <v>46311.45833333334</v>
       </c>
       <c r="B46">
-        <v>719</v>
+        <v>40</v>
       </c>
       <c r="C46">
-        <v>427</v>
+        <v>214</v>
       </c>
       <c r="D46">
-        <v>363.0523416653321</v>
+        <v>760.2927389961463</v>
       </c>
       <c r="E46">
-        <v>1146</v>
+        <v>254</v>
       </c>
     </row>
     <row r="47" spans="1:5">
       <c r="A47" s="2">
-        <v>46309.46875</v>
+        <v>46311.46875</v>
       </c>
       <c r="B47">
-        <v>716</v>
+        <v>40</v>
       </c>
       <c r="C47">
-        <v>429</v>
+        <v>216</v>
       </c>
       <c r="D47">
-        <v>355.7881095413863</v>
+        <v>712.3985790087739</v>
       </c>
       <c r="E47">
-        <v>1145</v>
+        <v>256</v>
       </c>
     </row>
     <row r="48" spans="1:5">
       <c r="A48" s="2">
-        <v>46309.47916666666</v>
+        <v>46311.47916666666</v>
       </c>
       <c r="B48">
-        <v>714</v>
+        <v>40</v>
       </c>
       <c r="C48">
-        <v>437</v>
+        <v>217</v>
       </c>
       <c r="D48">
-        <v>348.5238774174406</v>
+        <v>664.5044190214015</v>
       </c>
       <c r="E48">
-        <v>1151</v>
+        <v>257</v>
       </c>
     </row>
     <row r="49" spans="1:5">
       <c r="A49" s="2">
-        <v>46309.48958333334</v>
+        <v>46311.48958333334</v>
       </c>
       <c r="B49">
-        <v>683</v>
+        <v>39</v>
       </c>
       <c r="C49">
-        <v>459</v>
+        <v>215</v>
       </c>
       <c r="D49">
-        <v>341.2596452934949</v>
+        <v>616.6102590340291</v>
       </c>
       <c r="E49">
-        <v>1142</v>
+        <v>254</v>
       </c>
     </row>
     <row r="50" spans="1:5">
       <c r="A50" s="2">
-        <v>46309.5</v>
+        <v>46311.5</v>
       </c>
       <c r="B50">
-        <v>447</v>
+        <v>42</v>
       </c>
       <c r="C50">
-        <v>455</v>
+        <v>204</v>
       </c>
       <c r="D50">
-        <v>333.9954131695492</v>
+        <v>568.7160990466567</v>
       </c>
       <c r="E50">
-        <v>902</v>
+        <v>246</v>
       </c>
     </row>
     <row r="51" spans="1:5">
       <c r="A51" s="2">
-        <v>46309.51041666666</v>
+        <v>46311.51041666666</v>
       </c>
       <c r="B51">
-        <v>432</v>
+        <v>42</v>
       </c>
       <c r="C51">
-        <v>453</v>
+        <v>0</v>
       </c>
       <c r="D51">
-        <v>337.1718557182582</v>
+        <v>549.7178924214277</v>
       </c>
       <c r="E51">
-        <v>885</v>
+        <v>42</v>
       </c>
     </row>
     <row r="52" spans="1:5">
       <c r="A52" s="2">
-        <v>46309.52083333334</v>
+        <v>46311.52083333334</v>
       </c>
       <c r="B52">
-        <v>415</v>
+        <v>39</v>
       </c>
       <c r="C52">
-        <v>448</v>
+        <v>0</v>
       </c>
       <c r="D52">
-        <v>340.3482982669672</v>
+        <v>530.7196857961987</v>
       </c>
       <c r="E52">
-        <v>863</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5">
-      <c r="A53" s="2">
-        <v>46309.53125</v>
-      </c>
-      <c r="B53">
-        <v>224</v>
-      </c>
-      <c r="C53">
-        <v>379</v>
-      </c>
-      <c r="D53">
-        <v>343.5247408156761</v>
-      </c>
-      <c r="E53">
-        <v>603</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5">
-      <c r="A54" s="2">
-        <v>46309.54166666666</v>
-      </c>
-      <c r="B54">
-        <v>238</v>
-      </c>
-      <c r="C54">
-        <v>305</v>
-      </c>
-      <c r="D54">
-        <v>346.701183364385</v>
-      </c>
-      <c r="E54">
-        <v>543</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5">
-      <c r="A55" s="2">
-        <v>46309.55208333334</v>
-      </c>
-      <c r="B55">
-        <v>174</v>
-      </c>
-      <c r="C55">
-        <v>269</v>
-      </c>
-      <c r="D55">
-        <v>340.7199155011359</v>
-      </c>
-      <c r="E55">
-        <v>443</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5">
-      <c r="A56" s="2">
-        <v>46309.5625</v>
-      </c>
-      <c r="B56">
-        <v>164</v>
-      </c>
-      <c r="C56">
-        <v>266</v>
-      </c>
-      <c r="D56">
-        <v>334.7386476378866</v>
-      </c>
-      <c r="E56">
-        <v>430</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5">
-      <c r="A57" s="2">
-        <v>46309.57291666666</v>
-      </c>
-      <c r="B57">
-        <v>291</v>
-      </c>
-      <c r="C57">
-        <v>278</v>
-      </c>
-      <c r="D57">
-        <v>328.7573797746375</v>
-      </c>
-      <c r="E57">
-        <v>569</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5">
-      <c r="A58" s="2">
-        <v>46309.58333333334</v>
-      </c>
-      <c r="B58">
-        <v>151</v>
-      </c>
-      <c r="C58">
-        <v>329</v>
-      </c>
-      <c r="D58">
-        <v>322.7761119113883</v>
-      </c>
-      <c r="E58">
-        <v>480</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5">
-      <c r="A59" s="2">
-        <v>46309.59375</v>
-      </c>
-      <c r="B59">
-        <v>160</v>
-      </c>
-      <c r="C59">
-        <v>330</v>
-      </c>
-      <c r="D59">
-        <v>334.1192855811037</v>
-      </c>
-      <c r="E59">
-        <v>490</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5">
-      <c r="A60" s="2">
-        <v>46309.60416666666</v>
-      </c>
-      <c r="B60">
-        <v>137</v>
-      </c>
-      <c r="C60">
-        <v>0</v>
-      </c>
-      <c r="D60">
-        <v>345.4624592508191</v>
-      </c>
-      <c r="E60">
-        <v>137</v>
+        <v>39</v>
       </c>
     </row>
   </sheetData>

--- a/data_fetching/Entsoe/Hydro_Production.xlsx
+++ b/data_fetching/Entsoe/Hydro_Production.xlsx
@@ -390,7 +390,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E52"/>
+  <dimension ref="A1:E36"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:5">
@@ -412,869 +412,597 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="2">
-        <v>46311</v>
+        <v>46316</v>
       </c>
       <c r="B2">
-        <v>737</v>
+        <v>150</v>
       </c>
       <c r="C2">
-        <v>420</v>
+        <v>246</v>
       </c>
       <c r="D2">
-        <v>1167.045709619204</v>
+        <v>1190.31774149137</v>
       </c>
       <c r="E2">
-        <v>1157</v>
+        <v>396</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="2">
-        <v>46311.01041666666</v>
+        <v>46316.01041666666</v>
       </c>
       <c r="B3">
-        <v>733</v>
+        <v>130</v>
       </c>
       <c r="C3">
-        <v>417</v>
+        <v>224</v>
       </c>
       <c r="D3">
-        <v>1141.646428579514</v>
+        <v>1166.069874800561</v>
       </c>
       <c r="E3">
-        <v>1150</v>
+        <v>354</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="2">
-        <v>46311.02083333334</v>
+        <v>46316.02083333334</v>
       </c>
       <c r="B4">
-        <v>734</v>
+        <v>130</v>
       </c>
       <c r="C4">
-        <v>417</v>
+        <v>224</v>
       </c>
       <c r="D4">
-        <v>1116.247147539824</v>
+        <v>1141.822008109751</v>
       </c>
       <c r="E4">
-        <v>1151</v>
+        <v>354</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="2">
-        <v>46311.03125</v>
+        <v>46316.03125</v>
       </c>
       <c r="B5">
-        <v>730</v>
+        <v>152</v>
       </c>
       <c r="C5">
-        <v>417</v>
+        <v>224</v>
       </c>
       <c r="D5">
-        <v>1090.847866500133</v>
+        <v>1117.574141418941</v>
       </c>
       <c r="E5">
-        <v>1147</v>
+        <v>376</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="2">
-        <v>46311.04166666666</v>
+        <v>46316.04166666666</v>
       </c>
       <c r="B6">
-        <v>452</v>
+        <v>463</v>
       </c>
       <c r="C6">
-        <v>418</v>
+        <v>224</v>
       </c>
       <c r="D6">
-        <v>1065.448585460443</v>
+        <v>1093.326274728132</v>
       </c>
       <c r="E6">
-        <v>870</v>
+        <v>687</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="2">
-        <v>46311.05208333334</v>
+        <v>46316.05208333334</v>
       </c>
       <c r="B7">
-        <v>447</v>
+        <v>467</v>
       </c>
       <c r="C7">
-        <v>418</v>
+        <v>224</v>
       </c>
       <c r="D7">
-        <v>1061.507710465047</v>
+        <v>1058.3493610659</v>
       </c>
       <c r="E7">
-        <v>865</v>
+        <v>691</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="2">
-        <v>46311.0625</v>
+        <v>46316.0625</v>
       </c>
       <c r="B8">
-        <v>448</v>
+        <v>470</v>
       </c>
       <c r="C8">
-        <v>417</v>
+        <v>224</v>
       </c>
       <c r="D8">
-        <v>1057.566835469651</v>
+        <v>1023.372447403668</v>
       </c>
       <c r="E8">
-        <v>865</v>
+        <v>694</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="2">
-        <v>46311.07291666666</v>
+        <v>46316.07291666666</v>
       </c>
       <c r="B9">
-        <v>447</v>
+        <v>473</v>
       </c>
       <c r="C9">
-        <v>417</v>
+        <v>224</v>
       </c>
       <c r="D9">
-        <v>1053.625960474256</v>
+        <v>988.3955337414354</v>
       </c>
       <c r="E9">
-        <v>864</v>
+        <v>697</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="2">
-        <v>46311.08333333334</v>
+        <v>46316.08333333334</v>
       </c>
       <c r="B10">
-        <v>444</v>
+        <v>799</v>
       </c>
       <c r="C10">
-        <v>412</v>
+        <v>227</v>
       </c>
       <c r="D10">
-        <v>1049.68508547886</v>
+        <v>953.4186200792034</v>
       </c>
       <c r="E10">
-        <v>856</v>
+        <v>1026</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="2">
-        <v>46311.09375</v>
+        <v>46316.09375</v>
       </c>
       <c r="B11">
-        <v>443</v>
+        <v>896</v>
       </c>
       <c r="C11">
-        <v>412</v>
+        <v>275</v>
       </c>
       <c r="D11">
-        <v>996.6882896593106</v>
+        <v>936.0735112548998</v>
       </c>
       <c r="E11">
-        <v>855</v>
+        <v>1171</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="2">
-        <v>46311.10416666666</v>
+        <v>46316.10416666666</v>
       </c>
       <c r="B12">
-        <v>443</v>
+        <v>910</v>
       </c>
       <c r="C12">
-        <v>412</v>
+        <v>275</v>
       </c>
       <c r="D12">
-        <v>943.6914938397615</v>
+        <v>918.7284024305961</v>
       </c>
       <c r="E12">
-        <v>855</v>
+        <v>1185</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="2">
-        <v>46311.11458333334</v>
+        <v>46316.11458333334</v>
       </c>
       <c r="B13">
-        <v>444</v>
+        <v>903</v>
       </c>
       <c r="C13">
-        <v>412</v>
+        <v>274</v>
       </c>
       <c r="D13">
-        <v>890.6946980202123</v>
+        <v>901.3832936062925</v>
       </c>
       <c r="E13">
-        <v>856</v>
+        <v>1177</v>
       </c>
     </row>
     <row r="14" spans="1:5">
       <c r="A14" s="2">
-        <v>46311.125</v>
+        <v>46316.125</v>
       </c>
       <c r="B14">
-        <v>414</v>
+        <v>806</v>
       </c>
       <c r="C14">
-        <v>403</v>
+        <v>276</v>
       </c>
       <c r="D14">
-        <v>837.6979022006632</v>
+        <v>884.0381847819889</v>
       </c>
       <c r="E14">
-        <v>817</v>
+        <v>1082</v>
       </c>
     </row>
     <row r="15" spans="1:5">
       <c r="A15" s="2">
-        <v>46311.13541666666</v>
+        <v>46316.13541666666</v>
       </c>
       <c r="B15">
-        <v>413</v>
+        <v>697</v>
       </c>
       <c r="C15">
-        <v>403</v>
+        <v>276</v>
       </c>
       <c r="D15">
-        <v>843.1991814571652</v>
+        <v>896.2889259795739</v>
       </c>
       <c r="E15">
-        <v>816</v>
+        <v>973</v>
       </c>
     </row>
     <row r="16" spans="1:5">
       <c r="A16" s="2">
-        <v>46311.14583333334</v>
+        <v>46316.14583333334</v>
       </c>
       <c r="B16">
-        <v>412</v>
+        <v>787</v>
       </c>
       <c r="C16">
-        <v>403</v>
+        <v>275</v>
       </c>
       <c r="D16">
-        <v>848.7004607136672</v>
+        <v>908.539667177159</v>
       </c>
       <c r="E16">
-        <v>815</v>
+        <v>1062</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="2">
-        <v>46311.15625</v>
+        <v>46316.15625</v>
       </c>
       <c r="B17">
-        <v>419</v>
+        <v>878</v>
       </c>
       <c r="C17">
-        <v>402</v>
+        <v>275</v>
       </c>
       <c r="D17">
-        <v>854.2017399701692</v>
+        <v>920.7904083747441</v>
       </c>
       <c r="E17">
-        <v>821</v>
+        <v>1153</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="2">
-        <v>46311.16666666666</v>
+        <v>46316.16666666666</v>
       </c>
       <c r="B18">
-        <v>652</v>
+        <v>545</v>
       </c>
       <c r="C18">
-        <v>403</v>
+        <v>229</v>
       </c>
       <c r="D18">
-        <v>859.7030192266712</v>
+        <v>933.0411495723291</v>
       </c>
       <c r="E18">
-        <v>1055</v>
+        <v>774</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="2">
-        <v>46311.17708333334</v>
+        <v>46316.17708333334</v>
       </c>
       <c r="B19">
-        <v>666</v>
+        <v>644</v>
       </c>
       <c r="C19">
-        <v>403</v>
+        <v>272</v>
       </c>
       <c r="D19">
-        <v>934.032933157264</v>
+        <v>1031.46609640381</v>
       </c>
       <c r="E19">
-        <v>1069</v>
+        <v>916</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="2">
-        <v>46311.1875</v>
+        <v>46316.1875</v>
       </c>
       <c r="B20">
-        <v>677</v>
+        <v>644</v>
       </c>
       <c r="C20">
-        <v>403</v>
+        <v>275</v>
       </c>
       <c r="D20">
-        <v>1008.362847087857</v>
+        <v>1129.89104323529</v>
       </c>
       <c r="E20">
-        <v>1080</v>
+        <v>919</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="2">
-        <v>46311.19791666666</v>
+        <v>46316.19791666666</v>
       </c>
       <c r="B21">
-        <v>685</v>
+        <v>640</v>
       </c>
       <c r="C21">
-        <v>402</v>
+        <v>274</v>
       </c>
       <c r="D21">
-        <v>1082.69276101845</v>
+        <v>1228.315990066771</v>
       </c>
       <c r="E21">
-        <v>1087</v>
+        <v>914</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="2">
-        <v>46311.20833333334</v>
+        <v>46316.20833333334</v>
       </c>
       <c r="B22">
-        <v>822</v>
+        <v>741</v>
       </c>
       <c r="C22">
-        <v>417</v>
+        <v>315</v>
       </c>
       <c r="D22">
-        <v>1157.022674949042</v>
+        <v>1326.740936898251</v>
       </c>
       <c r="E22">
-        <v>1239</v>
+        <v>1056</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="2">
-        <v>46311.21875</v>
+        <v>46316.21875</v>
       </c>
       <c r="B23">
-        <v>828</v>
+        <v>753</v>
       </c>
       <c r="C23">
-        <v>420</v>
+        <v>326</v>
       </c>
       <c r="D23">
-        <v>1288.939478985624</v>
+        <v>1421.846826033226</v>
       </c>
       <c r="E23">
-        <v>1248</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="2">
-        <v>46311.22916666666</v>
+        <v>46316.22916666666</v>
       </c>
       <c r="B24">
-        <v>828</v>
+        <v>657</v>
       </c>
       <c r="C24">
-        <v>421</v>
+        <v>231</v>
       </c>
       <c r="D24">
-        <v>1420.856283022205</v>
+        <v>1516.9527151682</v>
       </c>
       <c r="E24">
-        <v>1249</v>
+        <v>888</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="2">
-        <v>46311.23958333334</v>
+        <v>46316.23958333334</v>
       </c>
       <c r="B25">
-        <v>836</v>
+        <v>669</v>
       </c>
       <c r="C25">
-        <v>421</v>
+        <v>229</v>
       </c>
       <c r="D25">
-        <v>1552.773087058786</v>
+        <v>1612.058604303174</v>
       </c>
       <c r="E25">
-        <v>1257</v>
+        <v>898</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="2">
-        <v>46311.25</v>
+        <v>46316.25</v>
       </c>
       <c r="B26">
-        <v>1008</v>
+        <v>923</v>
       </c>
       <c r="C26">
-        <v>416</v>
+        <v>559</v>
       </c>
       <c r="D26">
-        <v>1684.689891095368</v>
+        <v>1707.164493438149</v>
       </c>
       <c r="E26">
-        <v>1424</v>
+        <v>1482</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="2">
-        <v>46311.26041666666</v>
+        <v>46316.26041666666</v>
       </c>
       <c r="B27">
-        <v>1026</v>
+        <v>976</v>
       </c>
       <c r="C27">
-        <v>411</v>
+        <v>570</v>
       </c>
       <c r="D27">
-        <v>1720.860137801665</v>
+        <v>1745.765538759868</v>
       </c>
       <c r="E27">
-        <v>1437</v>
+        <v>1546</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="2">
-        <v>46311.27083333334</v>
+        <v>46316.27083333334</v>
       </c>
       <c r="B28">
-        <v>1019</v>
+        <v>947</v>
       </c>
       <c r="C28">
-        <v>414</v>
+        <v>570</v>
       </c>
       <c r="D28">
-        <v>1757.030384507962</v>
+        <v>1784.366584081587</v>
       </c>
       <c r="E28">
-        <v>1433</v>
+        <v>1517</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="2">
-        <v>46311.28125</v>
+        <v>46316.28125</v>
       </c>
       <c r="B29">
-        <v>1015</v>
+        <v>997</v>
       </c>
       <c r="C29">
-        <v>415</v>
+        <v>570</v>
       </c>
       <c r="D29">
-        <v>1793.20063121426</v>
+        <v>1822.967629403307</v>
       </c>
       <c r="E29">
-        <v>1430</v>
+        <v>1567</v>
       </c>
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="2">
-        <v>46311.29166666666</v>
+        <v>46316.29166666666</v>
       </c>
       <c r="B30">
-        <v>1040</v>
+        <v>1006</v>
       </c>
       <c r="C30">
-        <v>449</v>
+        <v>560</v>
       </c>
       <c r="D30">
-        <v>1829.370877920557</v>
+        <v>1861.568674725026</v>
       </c>
       <c r="E30">
-        <v>1489</v>
+        <v>1566</v>
       </c>
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="2">
-        <v>46311.30208333334</v>
+        <v>46316.30208333334</v>
       </c>
       <c r="B31">
-        <v>1027</v>
+        <v>1002</v>
       </c>
       <c r="C31">
-        <v>448</v>
+        <v>561</v>
       </c>
       <c r="D31">
-        <v>1788.154944442698</v>
+        <v>1824.731912564075</v>
       </c>
       <c r="E31">
-        <v>1475</v>
+        <v>1563</v>
       </c>
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="2">
-        <v>46311.3125</v>
+        <v>46316.3125</v>
       </c>
       <c r="B32">
-        <v>1024</v>
+        <v>1007</v>
       </c>
       <c r="C32">
-        <v>458</v>
+        <v>562</v>
       </c>
       <c r="D32">
-        <v>1746.939010964839</v>
+        <v>1787.895150403123</v>
       </c>
       <c r="E32">
-        <v>1482</v>
+        <v>1569</v>
       </c>
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="2">
-        <v>46311.32291666666</v>
+        <v>46316.32291666666</v>
       </c>
       <c r="B33">
-        <v>1022</v>
+        <v>1008</v>
       </c>
       <c r="C33">
-        <v>459</v>
+        <v>561</v>
       </c>
       <c r="D33">
-        <v>1705.72307748698</v>
+        <v>1751.058388242172</v>
       </c>
       <c r="E33">
-        <v>1481</v>
+        <v>1569</v>
       </c>
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="2">
-        <v>46311.33333333334</v>
+        <v>46316.33333333334</v>
       </c>
       <c r="B34">
-        <v>997</v>
+        <v>1012</v>
       </c>
       <c r="C34">
-        <v>446</v>
+        <v>539</v>
       </c>
       <c r="D34">
-        <v>1664.507144009121</v>
+        <v>1714.221626081221</v>
       </c>
       <c r="E34">
-        <v>1443</v>
+        <v>1551</v>
       </c>
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="2">
-        <v>46311.34375</v>
+        <v>46316.34375</v>
       </c>
       <c r="B35">
-        <v>987</v>
+        <v>1022</v>
       </c>
       <c r="C35">
-        <v>443</v>
+        <v>538</v>
       </c>
       <c r="D35">
-        <v>1570.757600404775</v>
+        <v>1653.30974995577</v>
       </c>
       <c r="E35">
-        <v>1430</v>
+        <v>1560</v>
       </c>
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="2">
-        <v>46311.35416666666</v>
+        <v>46316.35416666666</v>
       </c>
       <c r="B36">
-        <v>995</v>
+        <v>1042</v>
       </c>
       <c r="C36">
-        <v>445</v>
+        <v>582</v>
       </c>
       <c r="D36">
-        <v>1477.008056800429</v>
+        <v>1592.39787383032</v>
       </c>
       <c r="E36">
-        <v>1440</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37" s="2">
-        <v>46311.36458333334</v>
-      </c>
-      <c r="B37">
-        <v>983</v>
-      </c>
-      <c r="C37">
-        <v>457</v>
-      </c>
-      <c r="D37">
-        <v>1383.258513196084</v>
-      </c>
-      <c r="E37">
-        <v>1440</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38" s="2">
-        <v>46311.375</v>
-      </c>
-      <c r="B38">
-        <v>898</v>
-      </c>
-      <c r="C38">
-        <v>440</v>
-      </c>
-      <c r="D38">
-        <v>1289.508969591738</v>
-      </c>
-      <c r="E38">
-        <v>1338</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
-      <c r="A39" s="2">
-        <v>46311.38541666666</v>
-      </c>
-      <c r="B39">
-        <v>896</v>
-      </c>
-      <c r="C39">
-        <v>440</v>
-      </c>
-      <c r="D39">
-        <v>1156.920166639705</v>
-      </c>
-      <c r="E39">
-        <v>1336</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
-      <c r="A40" s="2">
-        <v>46311.39583333334</v>
-      </c>
-      <c r="B40">
-        <v>895</v>
-      </c>
-      <c r="C40">
-        <v>438</v>
-      </c>
-      <c r="D40">
-        <v>1024.331363687671</v>
-      </c>
-      <c r="E40">
-        <v>1333</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
-      <c r="A41" s="2">
-        <v>46311.40625</v>
-      </c>
-      <c r="B41">
-        <v>736</v>
-      </c>
-      <c r="C41">
-        <v>438</v>
-      </c>
-      <c r="D41">
-        <v>891.7425607356377</v>
-      </c>
-      <c r="E41">
-        <v>1174</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
-      <c r="A42" s="2">
-        <v>46311.41666666666</v>
-      </c>
-      <c r="B42">
-        <v>70</v>
-      </c>
-      <c r="C42">
-        <v>184</v>
-      </c>
-      <c r="D42">
-        <v>759.1537577836041</v>
-      </c>
-      <c r="E42">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
-      <c r="A43" s="2">
-        <v>46311.42708333334</v>
-      </c>
-      <c r="B43">
-        <v>51</v>
-      </c>
-      <c r="C43">
-        <v>208</v>
-      </c>
-      <c r="D43">
-        <v>759.4385030867396</v>
-      </c>
-      <c r="E43">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
-      <c r="A44" s="2">
-        <v>46311.4375</v>
-      </c>
-      <c r="B44">
-        <v>50</v>
-      </c>
-      <c r="C44">
-        <v>207</v>
-      </c>
-      <c r="D44">
-        <v>759.7232483898752</v>
-      </c>
-      <c r="E44">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5">
-      <c r="A45" s="2">
-        <v>46311.44791666666</v>
-      </c>
-      <c r="B45">
-        <v>48</v>
-      </c>
-      <c r="C45">
-        <v>207</v>
-      </c>
-      <c r="D45">
-        <v>760.0079936930108</v>
-      </c>
-      <c r="E45">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5">
-      <c r="A46" s="2">
-        <v>46311.45833333334</v>
-      </c>
-      <c r="B46">
-        <v>40</v>
-      </c>
-      <c r="C46">
-        <v>214</v>
-      </c>
-      <c r="D46">
-        <v>760.2927389961463</v>
-      </c>
-      <c r="E46">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5">
-      <c r="A47" s="2">
-        <v>46311.46875</v>
-      </c>
-      <c r="B47">
-        <v>40</v>
-      </c>
-      <c r="C47">
-        <v>216</v>
-      </c>
-      <c r="D47">
-        <v>712.3985790087739</v>
-      </c>
-      <c r="E47">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5">
-      <c r="A48" s="2">
-        <v>46311.47916666666</v>
-      </c>
-      <c r="B48">
-        <v>40</v>
-      </c>
-      <c r="C48">
-        <v>217</v>
-      </c>
-      <c r="D48">
-        <v>664.5044190214015</v>
-      </c>
-      <c r="E48">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5">
-      <c r="A49" s="2">
-        <v>46311.48958333334</v>
-      </c>
-      <c r="B49">
-        <v>39</v>
-      </c>
-      <c r="C49">
-        <v>215</v>
-      </c>
-      <c r="D49">
-        <v>616.6102590340291</v>
-      </c>
-      <c r="E49">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5">
-      <c r="A50" s="2">
-        <v>46311.5</v>
-      </c>
-      <c r="B50">
-        <v>42</v>
-      </c>
-      <c r="C50">
-        <v>204</v>
-      </c>
-      <c r="D50">
-        <v>568.7160990466567</v>
-      </c>
-      <c r="E50">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5">
-      <c r="A51" s="2">
-        <v>46311.51041666666</v>
-      </c>
-      <c r="B51">
-        <v>42</v>
-      </c>
-      <c r="C51">
-        <v>0</v>
-      </c>
-      <c r="D51">
-        <v>549.7178924214277</v>
-      </c>
-      <c r="E51">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5">
-      <c r="A52" s="2">
-        <v>46311.52083333334</v>
-      </c>
-      <c r="B52">
-        <v>39</v>
-      </c>
-      <c r="C52">
-        <v>0</v>
-      </c>
-      <c r="D52">
-        <v>530.7196857961987</v>
-      </c>
-      <c r="E52">
-        <v>39</v>
+        <v>1624</v>
       </c>
     </row>
   </sheetData>

--- a/data_fetching/Entsoe/Hydro_Production.xlsx
+++ b/data_fetching/Entsoe/Hydro_Production.xlsx
@@ -390,7 +390,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E36"/>
+  <dimension ref="A1:E39"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:5">
@@ -412,597 +412,648 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="2">
-        <v>46316</v>
+        <v>46320</v>
       </c>
       <c r="B2">
-        <v>150</v>
+        <v>644</v>
       </c>
       <c r="C2">
-        <v>246</v>
+        <v>516</v>
       </c>
       <c r="D2">
-        <v>1190.31774149137</v>
+        <v>845.9215962402436</v>
       </c>
       <c r="E2">
-        <v>396</v>
+        <v>1160</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="2">
-        <v>46316.01041666666</v>
+        <v>46320.01041666666</v>
       </c>
       <c r="B3">
-        <v>130</v>
+        <v>643</v>
       </c>
       <c r="C3">
-        <v>224</v>
+        <v>512</v>
       </c>
       <c r="D3">
-        <v>1166.069874800561</v>
+        <v>847.6379120773663</v>
       </c>
       <c r="E3">
-        <v>354</v>
+        <v>1155</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="2">
-        <v>46316.02083333334</v>
+        <v>46320.02083333334</v>
       </c>
       <c r="B4">
-        <v>130</v>
+        <v>643</v>
       </c>
       <c r="C4">
-        <v>224</v>
+        <v>512</v>
       </c>
       <c r="D4">
-        <v>1141.822008109751</v>
+        <v>849.3542279144891</v>
       </c>
       <c r="E4">
-        <v>354</v>
+        <v>1155</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="2">
-        <v>46316.03125</v>
+        <v>46320.03125</v>
       </c>
       <c r="B5">
-        <v>152</v>
+        <v>628</v>
       </c>
       <c r="C5">
-        <v>224</v>
+        <v>511</v>
       </c>
       <c r="D5">
-        <v>1117.574141418941</v>
+        <v>851.0705437516119</v>
       </c>
       <c r="E5">
-        <v>376</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="2">
-        <v>46316.04166666666</v>
+        <v>46320.04166666666</v>
       </c>
       <c r="B6">
-        <v>463</v>
+        <v>49</v>
       </c>
       <c r="C6">
-        <v>224</v>
+        <v>239</v>
       </c>
       <c r="D6">
-        <v>1093.326274728132</v>
+        <v>852.7868595887346</v>
       </c>
       <c r="E6">
-        <v>687</v>
+        <v>288</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="2">
-        <v>46316.05208333334</v>
+        <v>46320.05208333334</v>
       </c>
       <c r="B7">
-        <v>467</v>
+        <v>35</v>
       </c>
       <c r="C7">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="D7">
-        <v>1058.3493610659</v>
+        <v>847.9458393304972</v>
       </c>
       <c r="E7">
-        <v>691</v>
+        <v>258</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="2">
-        <v>46316.0625</v>
+        <v>46320.0625</v>
       </c>
       <c r="B8">
-        <v>470</v>
+        <v>36</v>
       </c>
       <c r="C8">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="D8">
-        <v>1023.372447403668</v>
+        <v>843.1048190722597</v>
       </c>
       <c r="E8">
-        <v>694</v>
+        <v>259</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="2">
-        <v>46316.07291666666</v>
+        <v>46320.07291666666</v>
       </c>
       <c r="B9">
-        <v>473</v>
+        <v>131</v>
       </c>
       <c r="C9">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="D9">
-        <v>988.3955337414354</v>
+        <v>838.2637988140224</v>
       </c>
       <c r="E9">
-        <v>697</v>
+        <v>358</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="2">
-        <v>46316.08333333334</v>
+        <v>46320.08333333334</v>
       </c>
       <c r="B10">
-        <v>799</v>
+        <v>131</v>
       </c>
       <c r="C10">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="D10">
-        <v>953.4186200792034</v>
+        <v>833.4227785557849</v>
       </c>
       <c r="E10">
-        <v>1026</v>
+        <v>359</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="2">
-        <v>46316.09375</v>
+        <v>46320.09375</v>
       </c>
       <c r="B11">
-        <v>896</v>
+        <v>131</v>
       </c>
       <c r="C11">
-        <v>275</v>
+        <v>228</v>
       </c>
       <c r="D11">
-        <v>936.0735112548998</v>
+        <v>833.4227785557849</v>
       </c>
       <c r="E11">
-        <v>1171</v>
+        <v>359</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="2">
-        <v>46316.10416666666</v>
+        <v>46320.10416666666</v>
       </c>
       <c r="B12">
-        <v>910</v>
+        <v>131</v>
       </c>
       <c r="C12">
-        <v>275</v>
+        <v>228</v>
       </c>
       <c r="D12">
-        <v>918.7284024305961</v>
+        <v>833.4227785557849</v>
       </c>
       <c r="E12">
-        <v>1185</v>
+        <v>359</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="2">
-        <v>46316.11458333334</v>
+        <v>46320.11458333334</v>
       </c>
       <c r="B13">
-        <v>903</v>
+        <v>131</v>
       </c>
       <c r="C13">
-        <v>274</v>
+        <v>228</v>
       </c>
       <c r="D13">
-        <v>901.3832936062925</v>
+        <v>833.4227785557849</v>
       </c>
       <c r="E13">
-        <v>1177</v>
+        <v>359</v>
       </c>
     </row>
     <row r="14" spans="1:5">
       <c r="A14" s="2">
-        <v>46316.125</v>
+        <v>46320.08333333334</v>
       </c>
       <c r="B14">
-        <v>806</v>
+        <v>131</v>
       </c>
       <c r="C14">
-        <v>276</v>
+        <v>228</v>
       </c>
       <c r="D14">
-        <v>884.0381847819889</v>
+        <v>833.4227785557849</v>
       </c>
       <c r="E14">
-        <v>1082</v>
+        <v>359</v>
       </c>
     </row>
     <row r="15" spans="1:5">
       <c r="A15" s="2">
-        <v>46316.13541666666</v>
+        <v>46320.09375</v>
       </c>
       <c r="B15">
-        <v>697</v>
+        <v>131</v>
       </c>
       <c r="C15">
-        <v>276</v>
+        <v>228</v>
       </c>
       <c r="D15">
-        <v>896.2889259795739</v>
+        <v>796.2544447065648</v>
       </c>
       <c r="E15">
-        <v>973</v>
+        <v>359</v>
       </c>
     </row>
     <row r="16" spans="1:5">
       <c r="A16" s="2">
-        <v>46316.14583333334</v>
+        <v>46320.10416666666</v>
       </c>
       <c r="B16">
-        <v>787</v>
+        <v>131</v>
       </c>
       <c r="C16">
-        <v>275</v>
+        <v>228</v>
       </c>
       <c r="D16">
-        <v>908.539667177159</v>
+        <v>759.0861108573447</v>
       </c>
       <c r="E16">
-        <v>1062</v>
+        <v>359</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="2">
-        <v>46316.15625</v>
+        <v>46320.11458333334</v>
       </c>
       <c r="B17">
-        <v>878</v>
+        <v>131</v>
       </c>
       <c r="C17">
-        <v>275</v>
+        <v>228</v>
       </c>
       <c r="D17">
-        <v>920.7904083747441</v>
+        <v>721.9177770081245</v>
       </c>
       <c r="E17">
-        <v>1153</v>
+        <v>359</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="2">
-        <v>46316.16666666666</v>
+        <v>46320.125</v>
       </c>
       <c r="B18">
-        <v>545</v>
+        <v>131</v>
       </c>
       <c r="C18">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="D18">
-        <v>933.0411495723291</v>
+        <v>684.7494431589043</v>
       </c>
       <c r="E18">
-        <v>774</v>
+        <v>359</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="2">
-        <v>46316.17708333334</v>
+        <v>46320.13541666666</v>
       </c>
       <c r="B19">
-        <v>644</v>
+        <v>32</v>
       </c>
       <c r="C19">
-        <v>272</v>
+        <v>227</v>
       </c>
       <c r="D19">
-        <v>1031.46609640381</v>
+        <v>782.9933808708074</v>
       </c>
       <c r="E19">
-        <v>916</v>
+        <v>259</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="2">
-        <v>46316.1875</v>
+        <v>46320.14583333334</v>
       </c>
       <c r="B20">
-        <v>644</v>
+        <v>32</v>
       </c>
       <c r="C20">
-        <v>275</v>
+        <v>227</v>
       </c>
       <c r="D20">
-        <v>1129.89104323529</v>
+        <v>881.2373185827106</v>
       </c>
       <c r="E20">
-        <v>919</v>
+        <v>259</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="2">
-        <v>46316.19791666666</v>
+        <v>46320.15625</v>
       </c>
       <c r="B21">
-        <v>640</v>
+        <v>31</v>
       </c>
       <c r="C21">
-        <v>274</v>
+        <v>227</v>
       </c>
       <c r="D21">
-        <v>1228.315990066771</v>
+        <v>979.4812562946138</v>
       </c>
       <c r="E21">
-        <v>914</v>
+        <v>258</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="2">
-        <v>46316.20833333334</v>
+        <v>46320.16666666666</v>
       </c>
       <c r="B22">
-        <v>741</v>
+        <v>52</v>
       </c>
       <c r="C22">
-        <v>315</v>
+        <v>229</v>
       </c>
       <c r="D22">
-        <v>1326.740936898251</v>
+        <v>1077.725194006517</v>
       </c>
       <c r="E22">
-        <v>1056</v>
+        <v>281</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="2">
-        <v>46316.21875</v>
+        <v>46320.17708333334</v>
       </c>
       <c r="B23">
-        <v>753</v>
+        <v>51</v>
       </c>
       <c r="C23">
-        <v>326</v>
+        <v>229</v>
       </c>
       <c r="D23">
-        <v>1421.846826033226</v>
+        <v>1204.459974614947</v>
       </c>
       <c r="E23">
-        <v>1079</v>
+        <v>280</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="2">
-        <v>46316.22916666666</v>
+        <v>46320.1875</v>
       </c>
       <c r="B24">
-        <v>657</v>
+        <v>54</v>
       </c>
       <c r="C24">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="D24">
-        <v>1516.9527151682</v>
+        <v>1331.194755223378</v>
       </c>
       <c r="E24">
-        <v>888</v>
+        <v>283</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="2">
-        <v>46316.23958333334</v>
+        <v>46320.19791666666</v>
       </c>
       <c r="B25">
-        <v>669</v>
+        <v>100</v>
       </c>
       <c r="C25">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="D25">
-        <v>1612.058604303174</v>
+        <v>1457.929535831808</v>
       </c>
       <c r="E25">
-        <v>898</v>
+        <v>334</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="2">
-        <v>46316.25</v>
+        <v>46320.20833333334</v>
       </c>
       <c r="B26">
-        <v>923</v>
+        <v>579</v>
       </c>
       <c r="C26">
-        <v>559</v>
+        <v>490</v>
       </c>
       <c r="D26">
-        <v>1707.164493438149</v>
+        <v>1584.664316440239</v>
       </c>
       <c r="E26">
-        <v>1482</v>
+        <v>1069</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="2">
-        <v>46316.26041666666</v>
+        <v>46320.21875</v>
       </c>
       <c r="B27">
-        <v>976</v>
+        <v>638</v>
       </c>
       <c r="C27">
-        <v>570</v>
+        <v>519</v>
       </c>
       <c r="D27">
-        <v>1745.765538759868</v>
+        <v>1620.868484627854</v>
       </c>
       <c r="E27">
-        <v>1546</v>
+        <v>1157</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="2">
-        <v>46316.27083333334</v>
+        <v>46320.22916666666</v>
       </c>
       <c r="B28">
-        <v>947</v>
+        <v>644</v>
       </c>
       <c r="C28">
-        <v>570</v>
+        <v>521</v>
       </c>
       <c r="D28">
-        <v>1784.366584081587</v>
+        <v>1657.072652815468</v>
       </c>
       <c r="E28">
-        <v>1517</v>
+        <v>1165</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="2">
-        <v>46316.28125</v>
+        <v>46320.23958333334</v>
       </c>
       <c r="B29">
-        <v>997</v>
+        <v>636</v>
       </c>
       <c r="C29">
-        <v>570</v>
+        <v>521</v>
       </c>
       <c r="D29">
-        <v>1822.967629403307</v>
+        <v>1693.276821003083</v>
       </c>
       <c r="E29">
-        <v>1567</v>
+        <v>1157</v>
       </c>
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="2">
-        <v>46316.29166666666</v>
+        <v>46320.25</v>
       </c>
       <c r="B30">
-        <v>1006</v>
+        <v>646</v>
       </c>
       <c r="C30">
-        <v>560</v>
+        <v>533</v>
       </c>
       <c r="D30">
-        <v>1861.568674725026</v>
+        <v>1729.480989190698</v>
       </c>
       <c r="E30">
-        <v>1566</v>
+        <v>1179</v>
       </c>
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="2">
-        <v>46316.30208333334</v>
+        <v>46320.26041666666</v>
       </c>
       <c r="B31">
-        <v>1002</v>
+        <v>647</v>
       </c>
       <c r="C31">
-        <v>561</v>
+        <v>532</v>
       </c>
       <c r="D31">
-        <v>1824.731912564075</v>
+        <v>1691.580697116907</v>
       </c>
       <c r="E31">
-        <v>1563</v>
+        <v>1179</v>
       </c>
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="2">
-        <v>46316.3125</v>
+        <v>46320.27083333334</v>
       </c>
       <c r="B32">
-        <v>1007</v>
+        <v>648</v>
       </c>
       <c r="C32">
-        <v>562</v>
+        <v>559</v>
       </c>
       <c r="D32">
-        <v>1787.895150403123</v>
+        <v>1653.680405043117</v>
       </c>
       <c r="E32">
-        <v>1569</v>
+        <v>1207</v>
       </c>
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="2">
-        <v>46316.32291666666</v>
+        <v>46320.28125</v>
       </c>
       <c r="B33">
-        <v>1008</v>
+        <v>645</v>
       </c>
       <c r="C33">
-        <v>561</v>
+        <v>568</v>
       </c>
       <c r="D33">
-        <v>1751.058388242172</v>
+        <v>1615.780112969327</v>
       </c>
       <c r="E33">
-        <v>1569</v>
+        <v>1213</v>
       </c>
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="2">
-        <v>46316.33333333334</v>
+        <v>46320.29166666666</v>
       </c>
       <c r="B34">
-        <v>1012</v>
+        <v>153</v>
       </c>
       <c r="C34">
-        <v>539</v>
+        <v>465</v>
       </c>
       <c r="D34">
-        <v>1714.221626081221</v>
+        <v>1577.879820895536</v>
       </c>
       <c r="E34">
-        <v>1551</v>
+        <v>618</v>
       </c>
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="2">
-        <v>46316.34375</v>
+        <v>46320.30208333334</v>
       </c>
       <c r="B35">
-        <v>1022</v>
+        <v>120</v>
       </c>
       <c r="C35">
-        <v>538</v>
+        <v>460</v>
       </c>
       <c r="D35">
-        <v>1653.30974995577</v>
+        <v>1488.358806026256</v>
       </c>
       <c r="E35">
-        <v>1560</v>
+        <v>580</v>
       </c>
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="2">
-        <v>46316.35416666666</v>
+        <v>46320.3125</v>
       </c>
       <c r="B36">
-        <v>1042</v>
+        <v>117</v>
       </c>
       <c r="C36">
+        <v>465</v>
+      </c>
+      <c r="D36">
+        <v>1398.837791156976</v>
+      </c>
+      <c r="E36">
         <v>582</v>
       </c>
-      <c r="D36">
-        <v>1592.39787383032</v>
-      </c>
-      <c r="E36">
-        <v>1624</v>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="2">
+        <v>46320.32291666666</v>
+      </c>
+      <c r="B37">
+        <v>115</v>
+      </c>
+      <c r="C37">
+        <v>465</v>
+      </c>
+      <c r="D37">
+        <v>1309.316776287695</v>
+      </c>
+      <c r="E37">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="2">
+        <v>46320.33333333334</v>
+      </c>
+      <c r="B38">
+        <v>126</v>
+      </c>
+      <c r="C38">
+        <v>455</v>
+      </c>
+      <c r="D38">
+        <v>1219.795761418415</v>
+      </c>
+      <c r="E38">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="2">
+        <v>46320.34375</v>
+      </c>
+      <c r="B39">
+        <v>125</v>
+      </c>
+      <c r="C39">
+        <v>451</v>
+      </c>
+      <c r="D39">
+        <v>1138.624118298081</v>
+      </c>
+      <c r="E39">
+        <v>576</v>
       </c>
     </row>
   </sheetData>
